--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Aircraft_Cumulative_Statistics_2022.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Aircraft_Cumulative_Statistics_2022.xlsx
@@ -13,78 +13,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Breeze</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-500</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A220-100</t>
+  </si>
+  <si>
+    <t>A220-300</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A320NEO</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B737-9</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A330-900</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B787-10</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -166,10 +205,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -189,40 +228,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -230,40 +269,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>46814806712</v>
+        <v>3443108090</v>
       </c>
       <c r="C2" s="0">
-        <v>55284184834</v>
+        <v>4193281495</v>
       </c>
       <c r="D2" s="0">
-        <v>670925</v>
+        <v>48947</v>
       </c>
       <c r="E2" s="0">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>238279</v>
+        <v>255629</v>
       </c>
       <c r="G2" s="0">
-        <v>2.8900000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="H2" s="0">
-        <v>9.9100000000000001</v>
+        <v>4.25</v>
       </c>
       <c r="I2" s="0">
-        <v>84.680000000000007</v>
+        <v>82.109999999999999</v>
       </c>
       <c r="J2" s="0">
-        <v>1368</v>
+        <v>328</v>
       </c>
       <c r="K2" s="0">
-        <v>5393</v>
+        <v>1971.6400000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>31.890000000000001</v>
+        <v>39.43</v>
       </c>
       <c r="M2" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.17100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -271,40 +310,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>15488171638</v>
+        <v>3324841614</v>
       </c>
       <c r="C3" s="0">
-        <v>18132647718</v>
+        <v>4199913235</v>
       </c>
       <c r="D3" s="0">
-        <v>435044</v>
+        <v>49376</v>
       </c>
       <c r="E3" s="0">
-        <v>176</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>114193</v>
+        <v>236283</v>
       </c>
       <c r="G3" s="0">
-        <v>2.7400000000000002</v>
+        <v>2.7799999999999998</v>
       </c>
       <c r="H3" s="0">
-        <v>6.5499999999999998</v>
+        <v>3.8900000000000001</v>
       </c>
       <c r="I3" s="0">
-        <v>85.420000000000002</v>
+        <v>79.159999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>900</v>
+        <v>356</v>
       </c>
       <c r="K3" s="0">
-        <v>5413</v>
+        <v>2087.2199999999998</v>
       </c>
       <c r="L3" s="0">
-        <v>30.710000000000001</v>
+        <v>41.75</v>
       </c>
       <c r="M3" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.16500000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -312,40 +351,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>191499465841</v>
+        <v>1649441888</v>
       </c>
       <c r="C4" s="0">
-        <v>229885903954</v>
+        <v>2041589717</v>
       </c>
       <c r="D4" s="0">
-        <v>705648</v>
+        <v>70351</v>
       </c>
       <c r="E4" s="0">
-        <v>173</v>
+        <v>69</v>
       </c>
       <c r="F4" s="0">
-        <v>1050971</v>
+        <v>56679</v>
       </c>
       <c r="G4" s="0">
-        <v>3.23</v>
+        <v>1.95</v>
       </c>
       <c r="H4" s="0">
-        <v>9.6199999999999992</v>
+        <v>3.71</v>
       </c>
       <c r="I4" s="0">
-        <v>83.299999999999997</v>
+        <v>80.790000000000006</v>
       </c>
       <c r="J4" s="0">
-        <v>1161</v>
+        <v>521</v>
       </c>
       <c r="K4" s="0">
-        <v>7518</v>
+        <v>1564.4300000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>40.869999999999997</v>
+        <v>22.600000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="5">
@@ -353,40 +392,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>647666426</v>
+        <v>30418448787</v>
       </c>
       <c r="C5" s="0">
-        <v>918104620</v>
+        <v>38044390377</v>
       </c>
       <c r="D5" s="0">
-        <v>65535</v>
+        <v>132131</v>
       </c>
       <c r="E5" s="0">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="F5" s="0">
-        <v>9416</v>
+        <v>891587</v>
       </c>
       <c r="G5" s="0">
-        <v>65535</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>65535</v>
+        <v>5.8399999999999999</v>
       </c>
       <c r="I5" s="0">
-        <v>70.540000000000006</v>
+        <v>79.959999999999994</v>
       </c>
       <c r="J5" s="0">
-        <v>806</v>
+        <v>568</v>
       </c>
       <c r="K5" s="0">
-        <v>0</v>
+        <v>1486.04</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
+        <v>19.780000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="6">
@@ -394,40 +433,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>181848269733</v>
+        <v>678924451</v>
       </c>
       <c r="C6" s="0">
-        <v>216006867346</v>
+        <v>894214450</v>
       </c>
       <c r="D6" s="0">
-        <v>694154</v>
+        <v>39778</v>
       </c>
       <c r="E6" s="0">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="F6" s="0">
-        <v>999532</v>
+        <v>52916</v>
       </c>
       <c r="G6" s="0">
-        <v>3.21</v>
+        <v>2.3500000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>9.2300000000000004</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>84.189999999999998</v>
+        <v>75.920000000000002</v>
       </c>
       <c r="J6" s="0">
-        <v>1136</v>
+        <v>338</v>
       </c>
       <c r="K6" s="0">
-        <v>6840</v>
+        <v>2549.9200000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>37.030000000000001</v>
+        <v>51</v>
       </c>
       <c r="M6" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +474,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>25643877882</v>
+        <v>6020332867</v>
       </c>
       <c r="C7" s="0">
-        <v>31714377680</v>
+        <v>7589997906</v>
       </c>
       <c r="D7" s="0">
-        <v>777694</v>
+        <v>107294</v>
       </c>
       <c r="E7" s="0">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="F7" s="0">
-        <v>165438</v>
+        <v>249985</v>
       </c>
       <c r="G7" s="0">
-        <v>4.0599999999999996</v>
+        <v>3.5299999999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>11.06</v>
+        <v>5.8799999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>80.859999999999999</v>
+        <v>79.319999999999993</v>
       </c>
       <c r="J7" s="0">
-        <v>990</v>
+        <v>461</v>
       </c>
       <c r="K7" s="0">
-        <v>5413</v>
+        <v>2360.3699999999999</v>
       </c>
       <c r="L7" s="0">
-        <v>27.949999999999999</v>
+        <v>35.810000000000002</v>
       </c>
       <c r="M7" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +515,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>14938665984</v>
+        <v>3872596484</v>
       </c>
       <c r="C8" s="0">
-        <v>18646481586</v>
+        <v>5063293832</v>
       </c>
       <c r="D8" s="0">
-        <v>836540</v>
+        <v>231201</v>
       </c>
       <c r="E8" s="0">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="F8" s="0">
-        <v>75622</v>
+        <v>91175</v>
       </c>
       <c r="G8" s="0">
-        <v>3.3900000000000001</v>
+        <v>4.1600000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>8.7300000000000004</v>
+        <v>7.6900000000000004</v>
       </c>
       <c r="I8" s="0">
-        <v>80.120000000000005</v>
+        <v>76.480000000000004</v>
       </c>
       <c r="J8" s="0">
-        <v>1053</v>
+        <v>550</v>
       </c>
       <c r="K8" s="0">
-        <v>8523</v>
+        <v>5566.4099999999999</v>
       </c>
       <c r="L8" s="0">
-        <v>38.43</v>
+        <v>55.159999999999997</v>
       </c>
       <c r="M8" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +556,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>52577079315</v>
+        <v>11542393484</v>
       </c>
       <c r="C9" s="0">
-        <v>64502706105</v>
+        <v>14430456129</v>
       </c>
       <c r="D9" s="0">
-        <v>620278</v>
+        <v>155551</v>
       </c>
       <c r="E9" s="0">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="F9" s="0">
-        <v>333701</v>
+        <v>413245</v>
       </c>
       <c r="G9" s="0">
-        <v>3.21</v>
+        <v>4.4500000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>10.130000000000001</v>
+        <v>7.4500000000000002</v>
       </c>
       <c r="I9" s="0">
-        <v>81.510000000000005</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J9" s="0">
-        <v>1210</v>
+        <v>462</v>
       </c>
       <c r="K9" s="0">
-        <v>5683</v>
+        <v>1806.5999999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>36.109999999999999</v>
+        <v>23.920000000000002</v>
       </c>
       <c r="M9" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +597,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>123865585444</v>
+        <v>5067144079</v>
       </c>
       <c r="C10" s="0">
-        <v>148494970073</v>
+        <v>6079867352</v>
       </c>
       <c r="D10" s="0">
-        <v>555121</v>
+        <v>378808</v>
       </c>
       <c r="E10" s="0">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="F10" s="0">
-        <v>1298423</v>
+        <v>60112</v>
       </c>
       <c r="G10" s="0">
-        <v>4.8499999999999996</v>
+        <v>3.75</v>
       </c>
       <c r="H10" s="0">
-        <v>9.6600000000000001</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="I10" s="0">
-        <v>83.409999999999997</v>
+        <v>83.340000000000003</v>
       </c>
       <c r="J10" s="0">
-        <v>728</v>
+        <v>928</v>
       </c>
       <c r="K10" s="0">
-        <v>4828</v>
+        <v>5072</v>
       </c>
       <c r="L10" s="0">
-        <v>30.809999999999999</v>
+        <v>46.549999999999997</v>
       </c>
       <c r="M10" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +638,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>39778287959</v>
+        <v>3573936749</v>
       </c>
       <c r="C11" s="0">
-        <v>48572965624</v>
+        <v>4416179862</v>
       </c>
       <c r="D11" s="0">
-        <v>736400</v>
+        <v>571304</v>
       </c>
       <c r="E11" s="0">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="F11" s="0">
-        <v>259625</v>
+        <v>32224</v>
       </c>
       <c r="G11" s="0">
-        <v>3.9399999999999999</v>
+        <v>4.1699999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>10.640000000000001</v>
+        <v>11.449999999999999</v>
       </c>
       <c r="I11" s="0">
-        <v>81.890000000000001</v>
+        <v>80.930000000000007</v>
       </c>
       <c r="J11" s="0">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="K11" s="0">
-        <v>4989</v>
+        <v>4544.6199999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>27.140000000000001</v>
+        <v>33.920000000000002</v>
       </c>
       <c r="M11" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +679,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>5215777397</v>
+        <v>39349587341</v>
       </c>
       <c r="C12" s="0">
-        <v>6705092128</v>
+        <v>47343104948</v>
       </c>
       <c r="D12" s="0">
-        <v>383148</v>
+        <v>389175</v>
       </c>
       <c r="E12" s="0">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="F12" s="0">
-        <v>31389</v>
+        <v>443965</v>
       </c>
       <c r="G12" s="0">
-        <v>1.79</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>5.3499999999999996</v>
+        <v>8.3499999999999996</v>
       </c>
       <c r="I12" s="0">
-        <v>77.790000000000006</v>
+        <v>83.120000000000005</v>
       </c>
       <c r="J12" s="0">
-        <v>1165</v>
+        <v>807</v>
       </c>
       <c r="K12" s="0">
-        <v>5995</v>
+        <v>5391.5299999999997</v>
       </c>
       <c r="L12" s="0">
-        <v>32.670000000000002</v>
+        <v>40.829999999999998</v>
       </c>
       <c r="M12" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.11600000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +720,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>190203737941</v>
+        <v>83578335923</v>
       </c>
       <c r="C13" s="0">
-        <v>228090827297</v>
+        <v>101045400311</v>
       </c>
       <c r="D13" s="0">
-        <v>751733</v>
+        <v>539657</v>
       </c>
       <c r="E13" s="0">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F13" s="0">
-        <v>775850</v>
+        <v>639310</v>
       </c>
       <c r="G13" s="0">
-        <v>2.5600000000000001</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>9.2100000000000009</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="I13" s="0">
-        <v>83.390000000000001</v>
+        <v>82.709999999999994</v>
       </c>
       <c r="J13" s="0">
-        <v>1495</v>
+        <v>964</v>
       </c>
       <c r="K13" s="0">
-        <v>7562</v>
+        <v>5828.9799999999996</v>
       </c>
       <c r="L13" s="0">
-        <v>39.630000000000003</v>
+        <v>35.609999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +761,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1327042228</v>
+        <v>30680565244</v>
       </c>
       <c r="C14" s="0">
-        <v>1588069800</v>
+        <v>37504083148</v>
       </c>
       <c r="D14" s="0">
-        <v>64477</v>
+        <v>744129</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="F14" s="0">
-        <v>77673</v>
+        <v>195899</v>
       </c>
       <c r="G14" s="0">
-        <v>3.1499999999999999</v>
+        <v>3.8900000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>4.9400000000000004</v>
+        <v>10.84</v>
       </c>
       <c r="I14" s="0">
-        <v>83.560000000000002</v>
+        <v>81.810000000000002</v>
       </c>
       <c r="J14" s="0">
-        <v>409</v>
+        <v>1039</v>
       </c>
       <c r="K14" s="0">
-        <v>1775</v>
+        <v>5113.46</v>
       </c>
       <c r="L14" s="0">
-        <v>35.5</v>
+        <v>27.739999999999998</v>
       </c>
       <c r="M14" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +802,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5348119841</v>
+        <v>109257934645</v>
       </c>
       <c r="C15" s="0">
-        <v>6940528769</v>
+        <v>127496473953</v>
       </c>
       <c r="D15" s="0">
-        <v>112689</v>
+        <v>766205</v>
       </c>
       <c r="E15" s="0">
-        <v>68</v>
+        <v>192</v>
       </c>
       <c r="F15" s="0">
-        <v>235833</v>
+        <v>590868</v>
       </c>
       <c r="G15" s="0">
-        <v>3.8300000000000001</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="H15" s="0">
-        <v>6.0899999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="I15" s="0">
-        <v>77.060000000000002</v>
+        <v>85.689999999999998</v>
       </c>
       <c r="J15" s="0">
-        <v>417</v>
+        <v>1152</v>
       </c>
       <c r="K15" s="0">
-        <v>1854</v>
+        <v>6355.1099999999997</v>
       </c>
       <c r="L15" s="0">
-        <v>26.510000000000002</v>
+        <v>33.740000000000002</v>
       </c>
       <c r="M15" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +843,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>7687341757</v>
+        <v>31642205471</v>
       </c>
       <c r="C16" s="0">
-        <v>9393408708</v>
+        <v>37519801450</v>
       </c>
       <c r="D16" s="0">
-        <v>56261</v>
+        <v>916011</v>
       </c>
       <c r="E16" s="0">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="F16" s="0">
-        <v>261319</v>
+        <v>103742</v>
       </c>
       <c r="G16" s="0">
-        <v>1.5700000000000001</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H16" s="0">
-        <v>2.71</v>
+        <v>11.109999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>81.840000000000003</v>
+        <v>84.329999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>510</v>
+        <v>1880</v>
       </c>
       <c r="K16" s="0">
-        <v>2020</v>
+        <v>6480.04</v>
       </c>
       <c r="L16" s="0">
-        <v>29.34</v>
+        <v>33.649999999999999</v>
       </c>
       <c r="M16" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +884,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>678924451</v>
+        <v>5511285241</v>
       </c>
       <c r="C17" s="0">
-        <v>894214450</v>
+        <v>6596500213</v>
       </c>
       <c r="D17" s="0">
-        <v>39778</v>
+        <v>225444</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="F17" s="0">
-        <v>52916</v>
+        <v>168809</v>
       </c>
       <c r="G17" s="0">
-        <v>2.3500000000000001</v>
+        <v>5.7699999999999996</v>
       </c>
       <c r="H17" s="0">
-        <v>3.6499999999999999</v>
+        <v>7.2400000000000002</v>
       </c>
       <c r="I17" s="0">
-        <v>75.920000000000002</v>
+        <v>83.549999999999997</v>
       </c>
       <c r="J17" s="0">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="K17" s="0">
-        <v>2550</v>
+        <v>5566.3900000000003</v>
       </c>
       <c r="L17" s="0">
-        <v>51</v>
+        <v>49.270000000000003</v>
       </c>
       <c r="M17" s="0">
-        <v>0.23000000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +925,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1576481803</v>
+        <v>68997588716</v>
       </c>
       <c r="C18" s="0">
-        <v>1925305568</v>
+        <v>83204426014</v>
       </c>
       <c r="D18" s="0">
-        <v>209272</v>
+        <v>463586</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="F18" s="0">
-        <v>46256</v>
+        <v>856733</v>
       </c>
       <c r="G18" s="0">
-        <v>5.0300000000000002</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H18" s="0">
-        <v>8.7400000000000002</v>
+        <v>9.1899999999999995</v>
       </c>
       <c r="I18" s="0">
-        <v>81.879999999999995</v>
+        <v>82.930000000000007</v>
       </c>
       <c r="J18" s="0">
-        <v>548</v>
+        <v>688</v>
       </c>
       <c r="K18" s="0">
-        <v>1546</v>
+        <v>5074.9499999999998</v>
       </c>
       <c r="L18" s="0">
-        <v>20.34</v>
+        <v>35.939999999999998</v>
       </c>
       <c r="M18" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +966,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>4967942041</v>
+        <v>145083313521</v>
       </c>
       <c r="C19" s="0">
-        <v>5783728526</v>
+        <v>173162167107</v>
       </c>
       <c r="D19" s="0">
-        <v>197061</v>
+        <v>582449</v>
       </c>
       <c r="E19" s="0">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="F19" s="0">
-        <v>120233</v>
+        <v>1063274</v>
       </c>
       <c r="G19" s="0">
-        <v>4.0999999999999996</v>
+        <v>3.5800000000000001</v>
       </c>
       <c r="H19" s="0">
-        <v>7.9400000000000004</v>
+        <v>9.0899999999999999</v>
       </c>
       <c r="I19" s="0">
-        <v>85.900000000000006</v>
+        <v>83.780000000000001</v>
       </c>
       <c r="J19" s="0">
-        <v>628</v>
+        <v>958</v>
       </c>
       <c r="K19" s="0">
-        <v>1588</v>
+        <v>5696.0500000000002</v>
       </c>
       <c r="L19" s="0">
-        <v>20.739999999999998</v>
+        <v>33.469999999999999</v>
       </c>
       <c r="M19" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +1007,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1054575762</v>
+        <v>32063929404</v>
       </c>
       <c r="C20" s="0">
-        <v>1285366524</v>
+        <v>38112249151</v>
       </c>
       <c r="D20" s="0">
-        <v>71768</v>
+        <v>702789</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F20" s="0">
-        <v>89093</v>
+        <v>209021</v>
       </c>
       <c r="G20" s="0">
-        <v>4.9699999999999998</v>
+        <v>3.8500000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>7.0199999999999996</v>
+        <v>10.460000000000001</v>
       </c>
       <c r="I20" s="0">
-        <v>82.040000000000006</v>
+        <v>84.129999999999995</v>
       </c>
       <c r="J20" s="0">
-        <v>289</v>
+        <v>1054</v>
       </c>
       <c r="K20" s="0">
-        <v>2136</v>
+        <v>5091.5600000000004</v>
       </c>
       <c r="L20" s="0">
-        <v>42.729999999999997</v>
+        <v>29.440000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1048,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>5154397478</v>
+        <v>3550385308</v>
       </c>
       <c r="C21" s="0">
-        <v>6395119229</v>
+        <v>4220746656</v>
       </c>
       <c r="D21" s="0">
-        <v>156935</v>
+        <v>481271</v>
       </c>
       <c r="E21" s="0">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F21" s="0">
-        <v>211341</v>
+        <v>24605</v>
       </c>
       <c r="G21" s="0">
-        <v>5.1900000000000004</v>
+        <v>2.8100000000000001</v>
       </c>
       <c r="H21" s="0">
-        <v>8.4000000000000004</v>
+        <v>7.2699999999999996</v>
       </c>
       <c r="I21" s="0">
-        <v>80.599999999999994</v>
+        <v>84.120000000000005</v>
       </c>
       <c r="J21" s="0">
-        <v>421</v>
+        <v>961</v>
       </c>
       <c r="K21" s="0">
-        <v>2248</v>
+        <v>5865.4899999999998</v>
       </c>
       <c r="L21" s="0">
-        <v>31.309999999999999</v>
+        <v>32.869999999999997</v>
       </c>
       <c r="M21" s="0">
-        <v>0.12</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1089,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>8617925827</v>
+        <v>81635074793</v>
       </c>
       <c r="C22" s="0">
-        <v>12109837910</v>
+        <v>94698340468</v>
       </c>
       <c r="D22" s="0">
-        <v>144872</v>
+        <v>701417</v>
       </c>
       <c r="E22" s="0">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="F22" s="0">
-        <v>316943</v>
+        <v>408462</v>
       </c>
       <c r="G22" s="0">
-        <v>3.79</v>
+        <v>3.0299999999999998</v>
       </c>
       <c r="H22" s="0">
-        <v>7.1600000000000001</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="I22" s="0">
-        <v>71.159999999999997</v>
+        <v>86.209999999999994</v>
       </c>
       <c r="J22" s="0">
-        <v>513</v>
+        <v>1294</v>
       </c>
       <c r="K22" s="0">
-        <v>1506</v>
+        <v>5743.8100000000004</v>
       </c>
       <c r="L22" s="0">
-        <v>20.23</v>
+        <v>32.07</v>
       </c>
       <c r="M22" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1130,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>20664739993</v>
+        <v>16119529387</v>
       </c>
       <c r="C23" s="0">
-        <v>25078263825</v>
+        <v>18601111942</v>
       </c>
       <c r="D23" s="0">
-        <v>115456</v>
+        <v>845505</v>
       </c>
       <c r="E23" s="0">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="F23" s="0">
-        <v>744717</v>
+        <v>65674</v>
       </c>
       <c r="G23" s="0">
-        <v>3.4300000000000002</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="H23" s="0">
-        <v>5.8200000000000003</v>
+        <v>11.43</v>
       </c>
       <c r="I23" s="0">
-        <v>82.400000000000006</v>
+        <v>86.659999999999997</v>
       </c>
       <c r="J23" s="0">
-        <v>494</v>
+        <v>1586</v>
       </c>
       <c r="K23" s="0">
-        <v>1623</v>
+        <v>4806.29</v>
       </c>
       <c r="L23" s="0">
-        <v>24</v>
+        <v>26.91</v>
       </c>
       <c r="M23" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="24">
@@ -1132,40 +1171,573 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
+        <v>23733255313</v>
+      </c>
+      <c r="C24" s="0">
+        <v>27734987977</v>
+      </c>
+      <c r="D24" s="0">
+        <v>548122</v>
+      </c>
+      <c r="E24" s="0">
+        <v>187</v>
+      </c>
+      <c r="F24" s="0">
+        <v>125762</v>
+      </c>
+      <c r="G24" s="0">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="H24" s="0">
+        <v>7.4900000000000002</v>
+      </c>
+      <c r="I24" s="0">
+        <v>85.569999999999993</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1198</v>
+      </c>
+      <c r="K24" s="0">
+        <v>7123.4399999999996</v>
+      </c>
+      <c r="L24" s="0">
+        <v>38.579999999999998</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.097000000000000003</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>8229152679</v>
+      </c>
+      <c r="C25" s="0">
+        <v>9484767210</v>
+      </c>
+      <c r="D25" s="0">
+        <v>706764</v>
+      </c>
+      <c r="E25" s="0">
+        <v>234</v>
+      </c>
+      <c r="F25" s="0">
+        <v>28521</v>
+      </c>
+      <c r="G25" s="0">
+        <v>2.1299999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>7.3399999999999999</v>
+      </c>
+      <c r="I25" s="0">
+        <v>86.760000000000005</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1421</v>
+      </c>
+      <c r="K25" s="0">
+        <v>7996.4700000000003</v>
+      </c>
+      <c r="L25" s="0">
+        <v>34.18</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.083000000000000004</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>22253940603</v>
+      </c>
+      <c r="C26" s="0">
+        <v>26525705951</v>
+      </c>
+      <c r="D26" s="0">
+        <v>909661</v>
+      </c>
+      <c r="E26" s="0">
+        <v>204</v>
+      </c>
+      <c r="F26" s="0">
+        <v>43583</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.49</v>
+      </c>
+      <c r="H26" s="0">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="I26" s="0">
+        <v>83.900000000000006</v>
+      </c>
+      <c r="J26" s="0">
+        <v>3018</v>
+      </c>
+      <c r="K26" s="0">
+        <v>9294.6900000000005</v>
+      </c>
+      <c r="L26" s="0">
+        <v>46.049999999999997</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>10769888047</v>
+      </c>
+      <c r="C27" s="0">
+        <v>13099503841</v>
+      </c>
+      <c r="D27" s="0">
+        <v>977575</v>
+      </c>
+      <c r="E27" s="0">
+        <v>237</v>
+      </c>
+      <c r="F27" s="0">
+        <v>17201</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1.28</v>
+      </c>
+      <c r="H27" s="0">
+        <v>8.8499999999999996</v>
+      </c>
+      <c r="I27" s="0">
+        <v>82.219999999999999</v>
+      </c>
+      <c r="J27" s="0">
+        <v>3214</v>
+      </c>
+      <c r="K27" s="0">
+        <v>9419.9899999999998</v>
+      </c>
+      <c r="L27" s="0">
+        <v>39.75</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.085000000000000006</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>14204654018</v>
+      </c>
+      <c r="C28" s="0">
+        <v>17805230856</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1400884</v>
+      </c>
+      <c r="E28" s="0">
+        <v>261</v>
+      </c>
+      <c r="F28" s="0">
+        <v>20891</v>
+      </c>
+      <c r="G28" s="0">
+        <v>1.6399999999999999</v>
+      </c>
+      <c r="H28" s="0">
+        <v>11.49</v>
+      </c>
+      <c r="I28" s="0">
+        <v>79.780000000000001</v>
+      </c>
+      <c r="J28" s="0">
+        <v>3298</v>
+      </c>
+      <c r="K28" s="0">
+        <v>10669.639999999999</v>
+      </c>
+      <c r="L28" s="0">
+        <v>41.229999999999997</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.086999999999999994</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>16033296402</v>
+      </c>
+      <c r="C29" s="0">
+        <v>19605485206</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1759918</v>
+      </c>
+      <c r="E29" s="0">
+        <v>286</v>
+      </c>
+      <c r="F29" s="0">
+        <v>17725</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.5900000000000001</v>
+      </c>
+      <c r="H29" s="0">
+        <v>12.84</v>
+      </c>
+      <c r="I29" s="0">
+        <v>81.780000000000001</v>
+      </c>
+      <c r="J29" s="0">
+        <v>3877</v>
+      </c>
+      <c r="K29" s="0">
+        <v>10316.07</v>
+      </c>
+      <c r="L29" s="0">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.074999999999999997</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>8195248673</v>
+      </c>
+      <c r="C30" s="0">
+        <v>10061535222</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1771397</v>
+      </c>
+      <c r="E30" s="0">
+        <v>281</v>
+      </c>
+      <c r="F30" s="0">
+        <v>8118</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="H30" s="0">
+        <v>12.98</v>
+      </c>
+      <c r="I30" s="0">
+        <v>81.450000000000003</v>
+      </c>
+      <c r="J30" s="0">
+        <v>4418</v>
+      </c>
+      <c r="K30" s="0">
+        <v>9914.2700000000004</v>
+      </c>
+      <c r="L30" s="0">
+        <v>35.340000000000003</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.072999999999999995</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>10407008850</v>
+      </c>
+      <c r="C31" s="0">
+        <v>13811522615</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1466191</v>
+      </c>
+      <c r="E31" s="0">
+        <v>307</v>
+      </c>
+      <c r="F31" s="0">
+        <v>8971</v>
+      </c>
+      <c r="G31" s="0">
+        <v>0.94999999999999996</v>
+      </c>
+      <c r="H31" s="0">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="I31" s="0">
+        <v>75.349999999999994</v>
+      </c>
+      <c r="J31" s="0">
+        <v>5038</v>
+      </c>
+      <c r="K31" s="0">
+        <v>10970.559999999999</v>
+      </c>
+      <c r="L31" s="0">
+        <v>35.890000000000001</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>14621513383</v>
+      </c>
+      <c r="C32" s="0">
+        <v>18069637897</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1299039</v>
+      </c>
+      <c r="E32" s="0">
+        <v>236</v>
+      </c>
+      <c r="F32" s="0">
+        <v>20544</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.48</v>
+      </c>
+      <c r="H32" s="0">
+        <v>11.18</v>
+      </c>
+      <c r="I32" s="0">
+        <v>80.920000000000002</v>
+      </c>
+      <c r="J32" s="0">
+        <v>3729</v>
+      </c>
+      <c r="K32" s="0">
+        <v>11865.719999999999</v>
+      </c>
+      <c r="L32" s="0">
+        <v>50.310000000000002</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>29071138713</v>
+      </c>
+      <c r="C33" s="0">
+        <v>37474068973</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1712709</v>
+      </c>
+      <c r="E33" s="0">
+        <v>266</v>
+      </c>
+      <c r="F33" s="0">
+        <v>29112</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="H33" s="0">
+        <v>12.859999999999999</v>
+      </c>
+      <c r="I33" s="0">
+        <v>77.579999999999998</v>
+      </c>
+      <c r="J33" s="0">
+        <v>4872</v>
+      </c>
+      <c r="K33" s="0">
+        <v>11515.91</v>
+      </c>
+      <c r="L33" s="0">
+        <v>43.57</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.085999999999999993</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>8471648174</v>
+      </c>
+      <c r="C34" s="0">
+        <v>9948819528</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1962292</v>
+      </c>
+      <c r="E34" s="0">
+        <v>318</v>
+      </c>
+      <c r="F34" s="0">
+        <v>8088</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="H34" s="0">
+        <v>12.470000000000001</v>
+      </c>
+      <c r="I34" s="0">
+        <v>85.150000000000006</v>
+      </c>
+      <c r="J34" s="0">
+        <v>3868</v>
+      </c>
+      <c r="K34" s="0">
+        <v>10133.42</v>
+      </c>
+      <c r="L34" s="0">
+        <v>31.870000000000001</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>39247149691</v>
+      </c>
+      <c r="C35" s="0">
+        <v>48373572968</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1141963</v>
+      </c>
+      <c r="E35" s="0">
+        <v>289</v>
+      </c>
+      <c r="F35" s="0">
+        <v>48332</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H35" s="0">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="I35" s="0">
+        <v>81.129999999999995</v>
+      </c>
+      <c r="J35" s="0">
+        <v>3552</v>
+      </c>
+      <c r="K35" s="0">
+        <v>14424.07</v>
+      </c>
+      <c r="L35" s="0">
+        <v>51.07</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>23300085420</v>
+      </c>
+      <c r="C36" s="0">
+        <v>29896544314</v>
+      </c>
+      <c r="D36" s="0">
+        <v>1947658</v>
+      </c>
+      <c r="E36" s="0">
+        <v>330</v>
+      </c>
+      <c r="F36" s="0">
+        <v>21718</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.4099999999999999</v>
+      </c>
+      <c r="H36" s="0">
+        <v>12</v>
+      </c>
+      <c r="I36" s="0">
+        <v>77.939999999999998</v>
+      </c>
+      <c r="J36" s="0">
+        <v>4187</v>
+      </c>
+      <c r="K36" s="0">
+        <v>15152.51</v>
+      </c>
+      <c r="L36" s="0">
+        <v>46.109999999999999</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.092999999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
         <v>945598883453</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C37" s="0">
         <v>1138348972274</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D37" s="0">
         <v>504554</v>
       </c>
-      <c r="E24" s="0">
+      <c r="E37" s="0">
         <v>139</v>
       </c>
-      <c r="F24" s="0">
+      <c r="F37" s="0">
         <v>7508763</v>
       </c>
-      <c r="G24" s="0">
+      <c r="G37" s="0">
         <v>3.3300000000000001</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H37" s="0">
         <v>8.2699999999999996</v>
       </c>
-      <c r="I24" s="0">
+      <c r="I37" s="0">
         <v>83.069999999999993</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J37" s="0">
         <v>915</v>
       </c>
-      <c r="K24" s="0">
-        <v>5538</v>
-      </c>
-      <c r="L24" s="0">
+      <c r="K37" s="0">
+        <v>5538.1599999999999</v>
+      </c>
+      <c r="L37" s="0">
         <v>35.289999999999999</v>
       </c>
-      <c r="M24" s="0">
-        <v>0.089999999999999997</v>
+      <c r="M37" s="0">
+        <v>0.090999999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Aircraft_Cumulative_Statistics_2022.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Aircraft_Cumulative_Statistics_2022.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="51">
   <si>
     <t>Row</t>
   </si>
@@ -30,7 +30,10 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -64,6 +67,9 @@
   </si>
   <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -205,7 +211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -228,40 +234,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -433,40 +439,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>678924451</v>
+        <v>733422490</v>
       </c>
       <c r="C6" s="0">
-        <v>894214450</v>
+        <v>947837800</v>
       </c>
       <c r="D6" s="0">
-        <v>39778</v>
+        <v>120132</v>
       </c>
       <c r="E6" s="0">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F6" s="0">
-        <v>52916</v>
+        <v>48195</v>
       </c>
       <c r="G6" s="0">
-        <v>2.3500000000000001</v>
+        <v>6.1100000000000003</v>
       </c>
       <c r="H6" s="0">
-        <v>3.6499999999999999</v>
+        <v>7.3399999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>75.920000000000002</v>
+        <v>77.379999999999995</v>
       </c>
       <c r="J6" s="0">
-        <v>338</v>
+        <v>259</v>
       </c>
       <c r="K6" s="0">
-        <v>2549.9200000000001</v>
+        <v>2263.1500000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>51</v>
+        <v>29.780000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.23400000000000001</v>
+        <v>0.13800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -474,40 +480,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6020332867</v>
+        <v>678924451</v>
       </c>
       <c r="C7" s="0">
-        <v>7589997906</v>
+        <v>894214450</v>
       </c>
       <c r="D7" s="0">
-        <v>107294</v>
+        <v>39778</v>
       </c>
       <c r="E7" s="0">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F7" s="0">
-        <v>249985</v>
+        <v>52916</v>
       </c>
       <c r="G7" s="0">
-        <v>3.5299999999999998</v>
+        <v>2.3500000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>5.8799999999999999</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>79.319999999999993</v>
+        <v>75.920000000000002</v>
       </c>
       <c r="J7" s="0">
-        <v>461</v>
+        <v>338</v>
       </c>
       <c r="K7" s="0">
-        <v>2360.3699999999999</v>
+        <v>2549.9200000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>35.810000000000002</v>
+        <v>51</v>
       </c>
       <c r="M7" s="0">
-        <v>0.129</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -515,40 +521,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>3872596484</v>
+        <v>6020332867</v>
       </c>
       <c r="C8" s="0">
-        <v>5063293832</v>
+        <v>7589997906</v>
       </c>
       <c r="D8" s="0">
-        <v>231201</v>
+        <v>107294</v>
       </c>
       <c r="E8" s="0">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="F8" s="0">
-        <v>91175</v>
+        <v>249985</v>
       </c>
       <c r="G8" s="0">
-        <v>4.1600000000000001</v>
+        <v>3.5299999999999998</v>
       </c>
       <c r="H8" s="0">
-        <v>7.6900000000000004</v>
+        <v>5.8799999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>76.480000000000004</v>
+        <v>79.319999999999993</v>
       </c>
       <c r="J8" s="0">
-        <v>550</v>
+        <v>461</v>
       </c>
       <c r="K8" s="0">
-        <v>5566.4099999999999</v>
+        <v>2360.3699999999999</v>
       </c>
       <c r="L8" s="0">
-        <v>55.159999999999997</v>
+        <v>35.810000000000002</v>
       </c>
       <c r="M8" s="0">
-        <v>0.185</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="9">
@@ -556,40 +562,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>11542393484</v>
+        <v>3872596484</v>
       </c>
       <c r="C9" s="0">
-        <v>14430456129</v>
+        <v>5063293832</v>
       </c>
       <c r="D9" s="0">
-        <v>155551</v>
+        <v>231201</v>
       </c>
       <c r="E9" s="0">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="F9" s="0">
-        <v>413245</v>
+        <v>91175</v>
       </c>
       <c r="G9" s="0">
-        <v>4.4500000000000002</v>
+        <v>4.1600000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>7.4500000000000002</v>
+        <v>7.6900000000000004</v>
       </c>
       <c r="I9" s="0">
-        <v>79.989999999999995</v>
+        <v>76.480000000000004</v>
       </c>
       <c r="J9" s="0">
-        <v>462</v>
+        <v>550</v>
       </c>
       <c r="K9" s="0">
-        <v>1806.5999999999999</v>
+        <v>5566.4099999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>23.920000000000002</v>
+        <v>55.159999999999997</v>
       </c>
       <c r="M9" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="10">
@@ -597,40 +603,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>5067144079</v>
+        <v>11542393484</v>
       </c>
       <c r="C10" s="0">
-        <v>6079867352</v>
+        <v>14430456129</v>
       </c>
       <c r="D10" s="0">
-        <v>378808</v>
+        <v>155551</v>
       </c>
       <c r="E10" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F10" s="0">
-        <v>60112</v>
+        <v>413245</v>
       </c>
       <c r="G10" s="0">
-        <v>3.75</v>
+        <v>4.4500000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>9.7100000000000009</v>
+        <v>7.4500000000000002</v>
       </c>
       <c r="I10" s="0">
-        <v>83.340000000000003</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J10" s="0">
-        <v>928</v>
+        <v>462</v>
       </c>
       <c r="K10" s="0">
-        <v>5072</v>
+        <v>1806.5999999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>46.549999999999997</v>
+        <v>23.920000000000002</v>
       </c>
       <c r="M10" s="0">
-        <v>0.13</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="11">
@@ -638,40 +644,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>3573936749</v>
+        <v>5067144079</v>
       </c>
       <c r="C11" s="0">
-        <v>4416179862</v>
+        <v>6079867352</v>
       </c>
       <c r="D11" s="0">
-        <v>571304</v>
+        <v>378808</v>
       </c>
       <c r="E11" s="0">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="F11" s="0">
-        <v>32224</v>
+        <v>60112</v>
       </c>
       <c r="G11" s="0">
-        <v>4.1699999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="H11" s="0">
-        <v>11.449999999999999</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="I11" s="0">
-        <v>80.930000000000007</v>
+        <v>83.340000000000003</v>
       </c>
       <c r="J11" s="0">
-        <v>1022</v>
+        <v>928</v>
       </c>
       <c r="K11" s="0">
-        <v>4544.6199999999999</v>
+        <v>5072</v>
       </c>
       <c r="L11" s="0">
-        <v>33.920000000000002</v>
+        <v>46.549999999999997</v>
       </c>
       <c r="M11" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="12">
@@ -679,40 +685,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>39349587341</v>
+        <v>3573936749</v>
       </c>
       <c r="C12" s="0">
-        <v>47343104948</v>
+        <v>4416179862</v>
       </c>
       <c r="D12" s="0">
-        <v>389175</v>
+        <v>571304</v>
       </c>
       <c r="E12" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F12" s="0">
-        <v>443965</v>
+        <v>32224</v>
       </c>
       <c r="G12" s="0">
-        <v>3.6499999999999999</v>
+        <v>4.1699999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>8.3499999999999996</v>
+        <v>11.449999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>83.120000000000005</v>
+        <v>80.930000000000007</v>
       </c>
       <c r="J12" s="0">
-        <v>807</v>
+        <v>1022</v>
       </c>
       <c r="K12" s="0">
-        <v>5391.5299999999997</v>
+        <v>4544.6199999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>40.829999999999998</v>
+        <v>33.920000000000002</v>
       </c>
       <c r="M12" s="0">
-        <v>0.11600000000000001</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="13">
@@ -720,40 +726,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>83578335923</v>
+        <v>39349587341</v>
       </c>
       <c r="C13" s="0">
-        <v>101045400311</v>
+        <v>47343104948</v>
       </c>
       <c r="D13" s="0">
-        <v>539657</v>
+        <v>389175</v>
       </c>
       <c r="E13" s="0">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="F13" s="0">
-        <v>639310</v>
+        <v>443965</v>
       </c>
       <c r="G13" s="0">
-        <v>3.4100000000000001</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>8.8800000000000008</v>
+        <v>8.3499999999999996</v>
       </c>
       <c r="I13" s="0">
-        <v>82.709999999999994</v>
+        <v>83.120000000000005</v>
       </c>
       <c r="J13" s="0">
-        <v>964</v>
+        <v>807</v>
       </c>
       <c r="K13" s="0">
-        <v>5828.9799999999996</v>
+        <v>5391.5299999999997</v>
       </c>
       <c r="L13" s="0">
-        <v>35.609999999999999</v>
+        <v>40.829999999999998</v>
       </c>
       <c r="M13" s="0">
-        <v>0.096000000000000002</v>
+        <v>0.11600000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -761,40 +767,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>30680565244</v>
+        <v>83578335923</v>
       </c>
       <c r="C14" s="0">
-        <v>37504083148</v>
+        <v>101045400311</v>
       </c>
       <c r="D14" s="0">
-        <v>744129</v>
+        <v>539657</v>
       </c>
       <c r="E14" s="0">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F14" s="0">
-        <v>195899</v>
+        <v>639310</v>
       </c>
       <c r="G14" s="0">
-        <v>3.8900000000000001</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>10.84</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="I14" s="0">
-        <v>81.810000000000002</v>
+        <v>82.709999999999994</v>
       </c>
       <c r="J14" s="0">
-        <v>1039</v>
+        <v>964</v>
       </c>
       <c r="K14" s="0">
-        <v>5113.46</v>
+        <v>5828.9799999999996</v>
       </c>
       <c r="L14" s="0">
-        <v>27.739999999999998</v>
+        <v>35.609999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="15">
@@ -802,40 +808,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>109257934645</v>
+        <v>30680565244</v>
       </c>
       <c r="C15" s="0">
-        <v>127496473953</v>
+        <v>37504083148</v>
       </c>
       <c r="D15" s="0">
-        <v>766205</v>
+        <v>744129</v>
       </c>
       <c r="E15" s="0">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F15" s="0">
-        <v>590868</v>
+        <v>195899</v>
       </c>
       <c r="G15" s="0">
-        <v>3.5499999999999998</v>
+        <v>3.8900000000000001</v>
       </c>
       <c r="H15" s="0">
-        <v>10.57</v>
+        <v>10.84</v>
       </c>
       <c r="I15" s="0">
-        <v>85.689999999999998</v>
+        <v>81.810000000000002</v>
       </c>
       <c r="J15" s="0">
-        <v>1152</v>
+        <v>1039</v>
       </c>
       <c r="K15" s="0">
-        <v>6355.1099999999997</v>
+        <v>5113.46</v>
       </c>
       <c r="L15" s="0">
-        <v>33.740000000000002</v>
+        <v>27.739999999999998</v>
       </c>
       <c r="M15" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="16">
@@ -843,40 +849,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>31642205471</v>
+        <v>109257934645</v>
       </c>
       <c r="C16" s="0">
-        <v>37519801450</v>
+        <v>127496473953</v>
       </c>
       <c r="D16" s="0">
-        <v>916011</v>
+        <v>766205</v>
       </c>
       <c r="E16" s="0">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F16" s="0">
-        <v>103742</v>
+        <v>590868</v>
       </c>
       <c r="G16" s="0">
-        <v>2.5299999999999998</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="H16" s="0">
-        <v>11.109999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="I16" s="0">
-        <v>84.329999999999998</v>
+        <v>85.689999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>1880</v>
+        <v>1152</v>
       </c>
       <c r="K16" s="0">
-        <v>6480.04</v>
+        <v>6355.1099999999997</v>
       </c>
       <c r="L16" s="0">
-        <v>33.649999999999999</v>
+        <v>33.740000000000002</v>
       </c>
       <c r="M16" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="17">
@@ -884,40 +890,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>5511285241</v>
+        <v>31642205471</v>
       </c>
       <c r="C17" s="0">
-        <v>6596500213</v>
+        <v>37519801450</v>
       </c>
       <c r="D17" s="0">
-        <v>225444</v>
+        <v>916011</v>
       </c>
       <c r="E17" s="0">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="F17" s="0">
-        <v>168809</v>
+        <v>103742</v>
       </c>
       <c r="G17" s="0">
-        <v>5.7699999999999996</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H17" s="0">
-        <v>7.2400000000000002</v>
+        <v>11.109999999999999</v>
       </c>
       <c r="I17" s="0">
-        <v>83.549999999999997</v>
+        <v>84.329999999999998</v>
       </c>
       <c r="J17" s="0">
-        <v>349</v>
+        <v>1880</v>
       </c>
       <c r="K17" s="0">
-        <v>5566.3900000000003</v>
+        <v>6480.04</v>
       </c>
       <c r="L17" s="0">
-        <v>49.270000000000003</v>
+        <v>33.649999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.17899999999999999</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -925,40 +931,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>68997588716</v>
+        <v>5511285241</v>
       </c>
       <c r="C18" s="0">
-        <v>83204426014</v>
+        <v>6596500213</v>
       </c>
       <c r="D18" s="0">
-        <v>463586</v>
+        <v>225444</v>
       </c>
       <c r="E18" s="0">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="F18" s="0">
-        <v>856733</v>
+        <v>168809</v>
       </c>
       <c r="G18" s="0">
-        <v>4.7699999999999996</v>
+        <v>5.7699999999999996</v>
       </c>
       <c r="H18" s="0">
-        <v>9.1899999999999995</v>
+        <v>7.2400000000000002</v>
       </c>
       <c r="I18" s="0">
-        <v>82.930000000000007</v>
+        <v>83.549999999999997</v>
       </c>
       <c r="J18" s="0">
-        <v>688</v>
+        <v>349</v>
       </c>
       <c r="K18" s="0">
-        <v>5074.9499999999998</v>
+        <v>5566.3900000000003</v>
       </c>
       <c r="L18" s="0">
-        <v>35.939999999999998</v>
+        <v>49.270000000000003</v>
       </c>
       <c r="M18" s="0">
-        <v>0.10100000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -966,40 +972,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>145083313521</v>
+        <v>196930</v>
       </c>
       <c r="C19" s="0">
-        <v>173162167107</v>
+        <v>359730</v>
       </c>
       <c r="D19" s="0">
-        <v>582449</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="F19" s="0">
-        <v>1063274</v>
+        <v>2</v>
       </c>
       <c r="G19" s="0">
-        <v>3.5800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H19" s="0">
-        <v>9.0899999999999999</v>
+        <v>0</v>
       </c>
       <c r="I19" s="0">
-        <v>83.780000000000001</v>
+        <v>54.740000000000002</v>
       </c>
       <c r="J19" s="0">
-        <v>958</v>
+        <v>1428</v>
       </c>
       <c r="K19" s="0">
-        <v>5696.0500000000002</v>
+        <v>2155466.3300000001</v>
       </c>
       <c r="L19" s="0">
-        <v>33.469999999999999</v>
+        <v>17106.880000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0.088999999999999996</v>
+        <v>39.146999999999998</v>
       </c>
     </row>
     <row r="20">
@@ -1007,40 +1013,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>32063929404</v>
+        <v>69615629790</v>
       </c>
       <c r="C20" s="0">
-        <v>38112249151</v>
+        <v>83964293367</v>
       </c>
       <c r="D20" s="0">
-        <v>702789</v>
+        <v>467820</v>
       </c>
       <c r="E20" s="0">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="F20" s="0">
-        <v>209021</v>
+        <v>862716</v>
       </c>
       <c r="G20" s="0">
-        <v>3.8500000000000001</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="H20" s="0">
-        <v>10.460000000000001</v>
+        <v>9.2699999999999996</v>
       </c>
       <c r="I20" s="0">
-        <v>84.129999999999995</v>
+        <v>82.909999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>1054</v>
+        <v>689</v>
       </c>
       <c r="K20" s="0">
-        <v>5091.5600000000004</v>
+        <v>5029.8500000000004</v>
       </c>
       <c r="L20" s="0">
-        <v>29.440000000000001</v>
+        <v>35.609999999999999</v>
       </c>
       <c r="M20" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1048,37 +1054,37 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>3550385308</v>
+        <v>145460307738</v>
       </c>
       <c r="C21" s="0">
-        <v>4220746656</v>
+        <v>173744007387</v>
       </c>
       <c r="D21" s="0">
-        <v>481271</v>
+        <v>584406</v>
       </c>
       <c r="E21" s="0">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F21" s="0">
-        <v>24605</v>
+        <v>1067771</v>
       </c>
       <c r="G21" s="0">
-        <v>2.8100000000000001</v>
+        <v>3.5899999999999999</v>
       </c>
       <c r="H21" s="0">
-        <v>7.2699999999999996</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="I21" s="0">
-        <v>84.120000000000005</v>
+        <v>83.719999999999999</v>
       </c>
       <c r="J21" s="0">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="K21" s="0">
-        <v>5865.4899999999998</v>
+        <v>5676.4399999999996</v>
       </c>
       <c r="L21" s="0">
-        <v>32.869999999999997</v>
+        <v>33.340000000000003</v>
       </c>
       <c r="M21" s="0">
         <v>0.088999999999999996</v>
@@ -1089,40 +1095,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>81635074793</v>
+        <v>32063929404</v>
       </c>
       <c r="C22" s="0">
-        <v>94698340468</v>
+        <v>38112249151</v>
       </c>
       <c r="D22" s="0">
-        <v>701417</v>
+        <v>702789</v>
       </c>
       <c r="E22" s="0">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F22" s="0">
-        <v>408462</v>
+        <v>209021</v>
       </c>
       <c r="G22" s="0">
-        <v>3.0299999999999998</v>
+        <v>3.8500000000000001</v>
       </c>
       <c r="H22" s="0">
-        <v>9.7799999999999994</v>
+        <v>10.460000000000001</v>
       </c>
       <c r="I22" s="0">
-        <v>86.209999999999994</v>
+        <v>84.129999999999995</v>
       </c>
       <c r="J22" s="0">
-        <v>1294</v>
+        <v>1054</v>
       </c>
       <c r="K22" s="0">
-        <v>5743.8100000000004</v>
+        <v>5091.5600000000004</v>
       </c>
       <c r="L22" s="0">
-        <v>32.07</v>
+        <v>29.440000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="23">
@@ -1130,40 +1136,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>16119529387</v>
+        <v>3550385308</v>
       </c>
       <c r="C23" s="0">
-        <v>18601111942</v>
+        <v>4220746656</v>
       </c>
       <c r="D23" s="0">
-        <v>845505</v>
+        <v>481271</v>
       </c>
       <c r="E23" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F23" s="0">
-        <v>65674</v>
+        <v>24605</v>
       </c>
       <c r="G23" s="0">
-        <v>2.9900000000000002</v>
+        <v>2.8100000000000001</v>
       </c>
       <c r="H23" s="0">
-        <v>11.43</v>
+        <v>7.2699999999999996</v>
       </c>
       <c r="I23" s="0">
-        <v>86.659999999999997</v>
+        <v>84.120000000000005</v>
       </c>
       <c r="J23" s="0">
-        <v>1586</v>
+        <v>961</v>
       </c>
       <c r="K23" s="0">
-        <v>4806.29</v>
+        <v>5865.4899999999998</v>
       </c>
       <c r="L23" s="0">
-        <v>26.91</v>
+        <v>32.869999999999997</v>
       </c>
       <c r="M23" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="24">
@@ -1171,40 +1177,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>23733255313</v>
+        <v>81635074793</v>
       </c>
       <c r="C24" s="0">
-        <v>27734987977</v>
+        <v>94698340468</v>
       </c>
       <c r="D24" s="0">
-        <v>548122</v>
+        <v>701417</v>
       </c>
       <c r="E24" s="0">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F24" s="0">
-        <v>125762</v>
+        <v>408462</v>
       </c>
       <c r="G24" s="0">
-        <v>2.4900000000000002</v>
+        <v>3.0299999999999998</v>
       </c>
       <c r="H24" s="0">
-        <v>7.4900000000000002</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="I24" s="0">
-        <v>85.569999999999993</v>
+        <v>86.209999999999994</v>
       </c>
       <c r="J24" s="0">
-        <v>1198</v>
+        <v>1294</v>
       </c>
       <c r="K24" s="0">
-        <v>7123.4399999999996</v>
+        <v>5743.8100000000004</v>
       </c>
       <c r="L24" s="0">
-        <v>38.579999999999998</v>
+        <v>32.07</v>
       </c>
       <c r="M24" s="0">
-        <v>0.097000000000000003</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="25">
@@ -1212,40 +1218,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>8229152679</v>
+        <v>16119529387</v>
       </c>
       <c r="C25" s="0">
-        <v>9484767210</v>
+        <v>18601111942</v>
       </c>
       <c r="D25" s="0">
-        <v>706764</v>
+        <v>845505</v>
       </c>
       <c r="E25" s="0">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="F25" s="0">
-        <v>28521</v>
+        <v>65674</v>
       </c>
       <c r="G25" s="0">
-        <v>2.1299999999999999</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="H25" s="0">
-        <v>7.3399999999999999</v>
+        <v>11.43</v>
       </c>
       <c r="I25" s="0">
-        <v>86.760000000000005</v>
+        <v>86.659999999999997</v>
       </c>
       <c r="J25" s="0">
-        <v>1421</v>
+        <v>1586</v>
       </c>
       <c r="K25" s="0">
-        <v>7996.4700000000003</v>
+        <v>4806.29</v>
       </c>
       <c r="L25" s="0">
-        <v>34.18</v>
+        <v>26.91</v>
       </c>
       <c r="M25" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="26">
@@ -1253,40 +1259,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>22253940603</v>
+        <v>23733255313</v>
       </c>
       <c r="C26" s="0">
-        <v>26525705951</v>
+        <v>27734987977</v>
       </c>
       <c r="D26" s="0">
-        <v>909661</v>
+        <v>548122</v>
       </c>
       <c r="E26" s="0">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="F26" s="0">
-        <v>43583</v>
+        <v>125762</v>
       </c>
       <c r="G26" s="0">
-        <v>1.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H26" s="0">
-        <v>9.7899999999999991</v>
+        <v>7.4900000000000002</v>
       </c>
       <c r="I26" s="0">
-        <v>83.900000000000006</v>
+        <v>85.569999999999993</v>
       </c>
       <c r="J26" s="0">
-        <v>3018</v>
+        <v>1198</v>
       </c>
       <c r="K26" s="0">
-        <v>9294.6900000000005</v>
+        <v>7123.4399999999996</v>
       </c>
       <c r="L26" s="0">
-        <v>46.049999999999997</v>
+        <v>38.579999999999998</v>
       </c>
       <c r="M26" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="27">
@@ -1294,40 +1300,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>10769888047</v>
+        <v>8229152679</v>
       </c>
       <c r="C27" s="0">
-        <v>13099503841</v>
+        <v>9484767210</v>
       </c>
       <c r="D27" s="0">
-        <v>977575</v>
+        <v>706764</v>
       </c>
       <c r="E27" s="0">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F27" s="0">
-        <v>17201</v>
+        <v>28521</v>
       </c>
       <c r="G27" s="0">
-        <v>1.28</v>
+        <v>2.1299999999999999</v>
       </c>
       <c r="H27" s="0">
-        <v>8.8499999999999996</v>
+        <v>7.3399999999999999</v>
       </c>
       <c r="I27" s="0">
-        <v>82.219999999999999</v>
+        <v>86.760000000000005</v>
       </c>
       <c r="J27" s="0">
-        <v>3214</v>
+        <v>1421</v>
       </c>
       <c r="K27" s="0">
-        <v>9419.9899999999998</v>
+        <v>7996.4700000000003</v>
       </c>
       <c r="L27" s="0">
-        <v>39.75</v>
+        <v>34.18</v>
       </c>
       <c r="M27" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="28">
@@ -1335,40 +1341,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>14204654018</v>
+        <v>22253940603</v>
       </c>
       <c r="C28" s="0">
-        <v>17805230856</v>
+        <v>26525705951</v>
       </c>
       <c r="D28" s="0">
-        <v>1400884</v>
+        <v>909661</v>
       </c>
       <c r="E28" s="0">
-        <v>261</v>
+        <v>204</v>
       </c>
       <c r="F28" s="0">
-        <v>20891</v>
+        <v>43583</v>
       </c>
       <c r="G28" s="0">
-        <v>1.6399999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="H28" s="0">
-        <v>11.49</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="I28" s="0">
-        <v>79.780000000000001</v>
+        <v>83.900000000000006</v>
       </c>
       <c r="J28" s="0">
-        <v>3298</v>
+        <v>3018</v>
       </c>
       <c r="K28" s="0">
-        <v>10669.639999999999</v>
+        <v>9294.6900000000005</v>
       </c>
       <c r="L28" s="0">
-        <v>41.229999999999997</v>
+        <v>46.049999999999997</v>
       </c>
       <c r="M28" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1376,40 +1382,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>16033296402</v>
+        <v>10769888047</v>
       </c>
       <c r="C29" s="0">
-        <v>19605485206</v>
+        <v>13099503841</v>
       </c>
       <c r="D29" s="0">
-        <v>1759918</v>
+        <v>977575</v>
       </c>
       <c r="E29" s="0">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="F29" s="0">
-        <v>17725</v>
+        <v>17201</v>
       </c>
       <c r="G29" s="0">
-        <v>1.5900000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="H29" s="0">
-        <v>12.84</v>
+        <v>8.8499999999999996</v>
       </c>
       <c r="I29" s="0">
-        <v>81.780000000000001</v>
+        <v>82.219999999999999</v>
       </c>
       <c r="J29" s="0">
-        <v>3877</v>
+        <v>3214</v>
       </c>
       <c r="K29" s="0">
-        <v>10316.07</v>
+        <v>9419.9899999999998</v>
       </c>
       <c r="L29" s="0">
-        <v>36.159999999999997</v>
+        <v>39.75</v>
       </c>
       <c r="M29" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="30">
@@ -1417,40 +1423,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>8195248673</v>
+        <v>14204654018</v>
       </c>
       <c r="C30" s="0">
-        <v>10061535222</v>
+        <v>17805230856</v>
       </c>
       <c r="D30" s="0">
-        <v>1771397</v>
+        <v>1400884</v>
       </c>
       <c r="E30" s="0">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="F30" s="0">
-        <v>8118</v>
+        <v>20891</v>
       </c>
       <c r="G30" s="0">
-        <v>1.4299999999999999</v>
+        <v>1.6399999999999999</v>
       </c>
       <c r="H30" s="0">
-        <v>12.98</v>
+        <v>11.49</v>
       </c>
       <c r="I30" s="0">
-        <v>81.450000000000003</v>
+        <v>79.780000000000001</v>
       </c>
       <c r="J30" s="0">
-        <v>4418</v>
+        <v>3298</v>
       </c>
       <c r="K30" s="0">
-        <v>9914.2700000000004</v>
+        <v>10669.639999999999</v>
       </c>
       <c r="L30" s="0">
-        <v>35.340000000000003</v>
+        <v>41.229999999999997</v>
       </c>
       <c r="M30" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="31">
@@ -1458,40 +1464,40 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>10407008850</v>
+        <v>16033296402</v>
       </c>
       <c r="C31" s="0">
-        <v>13811522615</v>
+        <v>19605485206</v>
       </c>
       <c r="D31" s="0">
-        <v>1466191</v>
+        <v>1759918</v>
       </c>
       <c r="E31" s="0">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="F31" s="0">
-        <v>8971</v>
+        <v>17725</v>
       </c>
       <c r="G31" s="0">
-        <v>0.94999999999999996</v>
+        <v>1.5900000000000001</v>
       </c>
       <c r="H31" s="0">
-        <v>9.5299999999999994</v>
+        <v>12.84</v>
       </c>
       <c r="I31" s="0">
-        <v>75.349999999999994</v>
+        <v>81.780000000000001</v>
       </c>
       <c r="J31" s="0">
-        <v>5038</v>
+        <v>3877</v>
       </c>
       <c r="K31" s="0">
-        <v>10970.559999999999</v>
+        <v>10316.07</v>
       </c>
       <c r="L31" s="0">
-        <v>35.890000000000001</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="M31" s="0">
-        <v>0.070999999999999994</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="32">
@@ -1499,40 +1505,40 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>14621513383</v>
+        <v>8195248673</v>
       </c>
       <c r="C32" s="0">
-        <v>18069637897</v>
+        <v>10061535222</v>
       </c>
       <c r="D32" s="0">
-        <v>1299039</v>
+        <v>1771397</v>
       </c>
       <c r="E32" s="0">
-        <v>236</v>
+        <v>281</v>
       </c>
       <c r="F32" s="0">
-        <v>20544</v>
+        <v>8118</v>
       </c>
       <c r="G32" s="0">
-        <v>1.48</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H32" s="0">
-        <v>11.18</v>
+        <v>12.98</v>
       </c>
       <c r="I32" s="0">
-        <v>80.920000000000002</v>
+        <v>81.450000000000003</v>
       </c>
       <c r="J32" s="0">
-        <v>3729</v>
+        <v>4418</v>
       </c>
       <c r="K32" s="0">
-        <v>11865.719999999999</v>
+        <v>9914.2700000000004</v>
       </c>
       <c r="L32" s="0">
-        <v>50.310000000000002</v>
+        <v>35.340000000000003</v>
       </c>
       <c r="M32" s="0">
-        <v>0.10199999999999999</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="33">
@@ -1540,40 +1546,40 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>29071138713</v>
+        <v>10407008850</v>
       </c>
       <c r="C33" s="0">
-        <v>37474068973</v>
+        <v>13811522615</v>
       </c>
       <c r="D33" s="0">
-        <v>1712709</v>
+        <v>1466191</v>
       </c>
       <c r="E33" s="0">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="F33" s="0">
-        <v>29112</v>
+        <v>8971</v>
       </c>
       <c r="G33" s="0">
-        <v>1.3300000000000001</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="H33" s="0">
-        <v>12.859999999999999</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="I33" s="0">
-        <v>77.579999999999998</v>
+        <v>75.349999999999994</v>
       </c>
       <c r="J33" s="0">
-        <v>4872</v>
+        <v>5038</v>
       </c>
       <c r="K33" s="0">
-        <v>11515.91</v>
+        <v>10970.559999999999</v>
       </c>
       <c r="L33" s="0">
-        <v>43.57</v>
+        <v>35.890000000000001</v>
       </c>
       <c r="M33" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="34">
@@ -1581,40 +1587,40 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>8471648174</v>
+        <v>14621513383</v>
       </c>
       <c r="C34" s="0">
-        <v>9948819528</v>
+        <v>18069637897</v>
       </c>
       <c r="D34" s="0">
-        <v>1962292</v>
+        <v>1299039</v>
       </c>
       <c r="E34" s="0">
-        <v>318</v>
+        <v>236</v>
       </c>
       <c r="F34" s="0">
-        <v>8088</v>
+        <v>20544</v>
       </c>
       <c r="G34" s="0">
-        <v>1.6000000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="H34" s="0">
-        <v>12.470000000000001</v>
+        <v>11.18</v>
       </c>
       <c r="I34" s="0">
-        <v>85.150000000000006</v>
+        <v>80.920000000000002</v>
       </c>
       <c r="J34" s="0">
-        <v>3868</v>
+        <v>3729</v>
       </c>
       <c r="K34" s="0">
-        <v>10133.42</v>
+        <v>11865.719999999999</v>
       </c>
       <c r="L34" s="0">
-        <v>31.870000000000001</v>
+        <v>50.310000000000002</v>
       </c>
       <c r="M34" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1622,40 +1628,40 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>39247149691</v>
+        <v>29071138713</v>
       </c>
       <c r="C35" s="0">
-        <v>48373572968</v>
+        <v>37474068973</v>
       </c>
       <c r="D35" s="0">
-        <v>1141963</v>
+        <v>1712709</v>
       </c>
       <c r="E35" s="0">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="F35" s="0">
-        <v>48332</v>
+        <v>29112</v>
       </c>
       <c r="G35" s="0">
-        <v>1.1399999999999999</v>
+        <v>1.3300000000000001</v>
       </c>
       <c r="H35" s="0">
-        <v>8.3699999999999992</v>
+        <v>12.859999999999999</v>
       </c>
       <c r="I35" s="0">
-        <v>81.129999999999995</v>
+        <v>77.579999999999998</v>
       </c>
       <c r="J35" s="0">
-        <v>3552</v>
+        <v>4872</v>
       </c>
       <c r="K35" s="0">
-        <v>14424.07</v>
+        <v>11515.91</v>
       </c>
       <c r="L35" s="0">
-        <v>51.07</v>
+        <v>43.57</v>
       </c>
       <c r="M35" s="0">
-        <v>0.106</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="36">
@@ -1663,40 +1669,40 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>23300085420</v>
+        <v>8471648174</v>
       </c>
       <c r="C36" s="0">
-        <v>29896544314</v>
+        <v>9948819528</v>
       </c>
       <c r="D36" s="0">
-        <v>1947658</v>
+        <v>1962292</v>
       </c>
       <c r="E36" s="0">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="F36" s="0">
-        <v>21718</v>
+        <v>8088</v>
       </c>
       <c r="G36" s="0">
-        <v>1.4099999999999999</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="H36" s="0">
-        <v>12</v>
+        <v>12.470000000000001</v>
       </c>
       <c r="I36" s="0">
-        <v>77.939999999999998</v>
+        <v>85.150000000000006</v>
       </c>
       <c r="J36" s="0">
-        <v>4187</v>
+        <v>3868</v>
       </c>
       <c r="K36" s="0">
-        <v>15152.51</v>
+        <v>10133.42</v>
       </c>
       <c r="L36" s="0">
-        <v>46.109999999999999</v>
+        <v>31.870000000000001</v>
       </c>
       <c r="M36" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1704,39 +1710,121 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>945598883453</v>
+        <v>39247149691</v>
       </c>
       <c r="C37" s="0">
-        <v>1138348972274</v>
+        <v>48373572968</v>
       </c>
       <c r="D37" s="0">
-        <v>504554</v>
+        <v>1141963</v>
       </c>
       <c r="E37" s="0">
-        <v>139</v>
+        <v>289</v>
       </c>
       <c r="F37" s="0">
-        <v>7508763</v>
+        <v>48332</v>
       </c>
       <c r="G37" s="0">
-        <v>3.3300000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="H37" s="0">
-        <v>8.2699999999999996</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="I37" s="0">
-        <v>83.069999999999993</v>
+        <v>81.129999999999995</v>
       </c>
       <c r="J37" s="0">
-        <v>915</v>
+        <v>3552</v>
       </c>
       <c r="K37" s="0">
-        <v>5538.1599999999999</v>
+        <v>14424.07</v>
       </c>
       <c r="L37" s="0">
-        <v>35.289999999999999</v>
+        <v>51.07</v>
       </c>
       <c r="M37" s="0">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>23300085420</v>
+      </c>
+      <c r="C38" s="0">
+        <v>29896544314</v>
+      </c>
+      <c r="D38" s="0">
+        <v>1947658</v>
+      </c>
+      <c r="E38" s="0">
+        <v>330</v>
+      </c>
+      <c r="F38" s="0">
+        <v>21718</v>
+      </c>
+      <c r="G38" s="0">
+        <v>1.4099999999999999</v>
+      </c>
+      <c r="H38" s="0">
+        <v>12</v>
+      </c>
+      <c r="I38" s="0">
+        <v>77.939999999999998</v>
+      </c>
+      <c r="J38" s="0">
+        <v>4187</v>
+      </c>
+      <c r="K38" s="0">
+        <v>15152.51</v>
+      </c>
+      <c r="L38" s="0">
+        <v>46.109999999999999</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0.092999999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>947327538164</v>
+      </c>
+      <c r="C39" s="0">
+        <v>1140638877437</v>
+      </c>
+      <c r="D39" s="0">
+        <v>503807</v>
+      </c>
+      <c r="E39" s="0">
+        <v>138</v>
+      </c>
+      <c r="F39" s="0">
+        <v>7567440</v>
+      </c>
+      <c r="G39" s="0">
+        <v>3.3399999999999999</v>
+      </c>
+      <c r="H39" s="0">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="I39" s="0">
+        <v>83.049999999999997</v>
+      </c>
+      <c r="J39" s="0">
+        <v>911</v>
+      </c>
+      <c r="K39" s="0">
+        <v>5521.6800000000003</v>
+      </c>
+      <c r="L39" s="0">
+        <v>35.240000000000002</v>
+      </c>
+      <c r="M39" s="0">
         <v>0.090999999999999998</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Aircraft_Cumulative_Statistics_2022.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Aircraft_Cumulative_Statistics_2022.xlsx
@@ -13,38 +13,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>E145</t>
-  </si>
-  <si>
-    <t>CRJ-200</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
-    <t>E175</t>
-  </si>
-  <si>
-    <t>Q400</t>
-  </si>
-  <si>
-    <t>CRJ-550</t>
-  </si>
-  <si>
-    <t>CRJ-700</t>
-  </si>
-  <si>
-    <t>E190</t>
-  </si>
-  <si>
-    <t>CRJ-900</t>
-  </si>
-  <si>
     <t>A220-100</t>
   </si>
   <si>
@@ -57,9 +30,6 @@
     <t>A320</t>
   </si>
   <si>
-    <t>A320NEO</t>
-  </si>
-  <si>
     <t>A321</t>
   </si>
   <si>
@@ -67,9 +37,6 @@
   </si>
   <si>
     <t>B717-200</t>
-  </si>
-  <si>
-    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -211,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -234,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -275,40 +242,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>3443108090</v>
+        <v>5067144079</v>
       </c>
       <c r="C2" s="0">
-        <v>4193281495</v>
+        <v>6079867352</v>
       </c>
       <c r="D2" s="0">
-        <v>48947</v>
+        <v>378808</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F2" s="0">
-        <v>255629</v>
+        <v>60112</v>
       </c>
       <c r="G2" s="0">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="H2" s="0">
-        <v>4.25</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="I2" s="0">
-        <v>82.109999999999999</v>
+        <v>83.340000000000003</v>
       </c>
       <c r="J2" s="0">
-        <v>328</v>
+        <v>928</v>
       </c>
       <c r="K2" s="0">
-        <v>1971.6400000000001</v>
+        <v>5072</v>
       </c>
       <c r="L2" s="0">
-        <v>39.43</v>
+        <v>46.549999999999997</v>
       </c>
       <c r="M2" s="0">
-        <v>0.17100000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="3">
@@ -316,40 +283,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>3324841614</v>
+        <v>1498417680</v>
       </c>
       <c r="C3" s="0">
-        <v>4199913235</v>
+        <v>1856232652</v>
       </c>
       <c r="D3" s="0">
-        <v>49376</v>
+        <v>465221</v>
       </c>
       <c r="E3" s="0">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F3" s="0">
-        <v>236283</v>
+        <v>16511</v>
       </c>
       <c r="G3" s="0">
-        <v>2.7799999999999998</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="H3" s="0">
-        <v>3.8900000000000001</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="I3" s="0">
-        <v>79.159999999999997</v>
+        <v>80.719999999999999</v>
       </c>
       <c r="J3" s="0">
-        <v>356</v>
+        <v>865</v>
       </c>
       <c r="K3" s="0">
-        <v>2087.2199999999998</v>
+        <v>5191.1899999999996</v>
       </c>
       <c r="L3" s="0">
-        <v>41.75</v>
+        <v>39.939999999999998</v>
       </c>
       <c r="M3" s="0">
-        <v>0.16500000000000001</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="4">
@@ -357,40 +324,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>1649441888</v>
+        <v>30941929922</v>
       </c>
       <c r="C4" s="0">
-        <v>2041589717</v>
+        <v>37212007506</v>
       </c>
       <c r="D4" s="0">
-        <v>70351</v>
+        <v>378748</v>
       </c>
       <c r="E4" s="0">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="F4" s="0">
-        <v>56679</v>
+        <v>368100</v>
       </c>
       <c r="G4" s="0">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="H4" s="0">
-        <v>3.71</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="I4" s="0">
-        <v>80.790000000000006</v>
+        <v>83.150000000000006</v>
       </c>
       <c r="J4" s="0">
-        <v>521</v>
+        <v>788</v>
       </c>
       <c r="K4" s="0">
-        <v>1564.4300000000001</v>
+        <v>5460.5299999999997</v>
       </c>
       <c r="L4" s="0">
-        <v>22.600000000000001</v>
+        <v>42.579999999999998</v>
       </c>
       <c r="M4" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="5">
@@ -398,40 +365,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>30418448787</v>
+        <v>27838245989</v>
       </c>
       <c r="C5" s="0">
-        <v>38044390377</v>
+        <v>33062369821</v>
       </c>
       <c r="D5" s="0">
-        <v>132131</v>
+        <v>448547</v>
       </c>
       <c r="E5" s="0">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="F5" s="0">
-        <v>891587</v>
+        <v>266033</v>
       </c>
       <c r="G5" s="0">
-        <v>3.1000000000000001</v>
+        <v>3.6099999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>5.8399999999999999</v>
+        <v>8.2699999999999996</v>
       </c>
       <c r="I5" s="0">
-        <v>79.959999999999994</v>
+        <v>84.200000000000003</v>
       </c>
       <c r="J5" s="0">
-        <v>568</v>
+        <v>817</v>
       </c>
       <c r="K5" s="0">
-        <v>1486.04</v>
+        <v>5969.1099999999997</v>
       </c>
       <c r="L5" s="0">
-        <v>19.780000000000001</v>
+        <v>39.259999999999998</v>
       </c>
       <c r="M5" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="6">
@@ -439,40 +406,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>733422490</v>
+        <v>78219629378</v>
       </c>
       <c r="C6" s="0">
-        <v>947837800</v>
+        <v>90032914266</v>
       </c>
       <c r="D6" s="0">
-        <v>120132</v>
+        <v>719055</v>
       </c>
       <c r="E6" s="0">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F6" s="0">
-        <v>48195</v>
+        <v>453389</v>
       </c>
       <c r="G6" s="0">
-        <v>6.1100000000000003</v>
+        <v>3.6200000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>7.3399999999999999</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>77.379999999999995</v>
+        <v>86.879999999999995</v>
       </c>
       <c r="J6" s="0">
-        <v>259</v>
+        <v>1079</v>
       </c>
       <c r="K6" s="0">
-        <v>2263.1500000000001</v>
+        <v>6761.4799999999996</v>
       </c>
       <c r="L6" s="0">
-        <v>29.780000000000001</v>
+        <v>36.609999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.13800000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="7">
@@ -480,40 +447,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>678924451</v>
+        <v>19050882775</v>
       </c>
       <c r="C7" s="0">
-        <v>894214450</v>
+        <v>22013931300</v>
       </c>
       <c r="D7" s="0">
-        <v>39778</v>
+        <v>968071</v>
       </c>
       <c r="E7" s="0">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="F7" s="0">
-        <v>52916</v>
+        <v>60703</v>
       </c>
       <c r="G7" s="0">
-        <v>2.3500000000000001</v>
+        <v>2.6699999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>3.6499999999999999</v>
+        <v>11.52</v>
       </c>
       <c r="I7" s="0">
-        <v>75.920000000000002</v>
+        <v>86.540000000000006</v>
       </c>
       <c r="J7" s="0">
-        <v>338</v>
+        <v>1853</v>
       </c>
       <c r="K7" s="0">
-        <v>2549.9200000000001</v>
+        <v>7309.04</v>
       </c>
       <c r="L7" s="0">
-        <v>51</v>
+        <v>37.340000000000003</v>
       </c>
       <c r="M7" s="0">
-        <v>0.23400000000000001</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="8">
@@ -521,40 +488,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>6020332867</v>
+        <v>4872401067</v>
       </c>
       <c r="C8" s="0">
-        <v>7589997906</v>
+        <v>5768444149</v>
       </c>
       <c r="D8" s="0">
-        <v>107294</v>
+        <v>258443</v>
       </c>
       <c r="E8" s="0">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="F8" s="0">
-        <v>249985</v>
+        <v>122348</v>
       </c>
       <c r="G8" s="0">
-        <v>3.5299999999999998</v>
+        <v>5.4800000000000004</v>
       </c>
       <c r="H8" s="0">
-        <v>5.8799999999999999</v>
+        <v>7.9199999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>79.319999999999993</v>
+        <v>84.469999999999999</v>
       </c>
       <c r="J8" s="0">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="K8" s="0">
-        <v>2360.3699999999999</v>
+        <v>5372.3800000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>35.810000000000002</v>
+        <v>48.850000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.129</v>
+        <v>0.16500000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -562,40 +529,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>3872596484</v>
+        <v>5619473832</v>
       </c>
       <c r="C9" s="0">
-        <v>5063293832</v>
+        <v>6713361774</v>
       </c>
       <c r="D9" s="0">
-        <v>231201</v>
+        <v>459505</v>
       </c>
       <c r="E9" s="0">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F9" s="0">
-        <v>91175</v>
+        <v>47561</v>
       </c>
       <c r="G9" s="0">
-        <v>4.1600000000000001</v>
+        <v>3.2599999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>7.6900000000000004</v>
+        <v>9.6500000000000004</v>
       </c>
       <c r="I9" s="0">
-        <v>76.480000000000004</v>
+        <v>83.709999999999994</v>
       </c>
       <c r="J9" s="0">
-        <v>550</v>
+        <v>1120</v>
       </c>
       <c r="K9" s="0">
-        <v>5566.4099999999999</v>
+        <v>7111.3999999999996</v>
       </c>
       <c r="L9" s="0">
-        <v>55.159999999999997</v>
+        <v>56.439999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.185</v>
+        <v>0.14899999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -603,40 +570,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>11542393484</v>
+        <v>85352738061</v>
       </c>
       <c r="C10" s="0">
-        <v>14430456129</v>
+        <v>101625092274</v>
       </c>
       <c r="D10" s="0">
-        <v>155551</v>
+        <v>557369</v>
       </c>
       <c r="E10" s="0">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="F10" s="0">
-        <v>413245</v>
+        <v>602430</v>
       </c>
       <c r="G10" s="0">
-        <v>4.4500000000000002</v>
+        <v>3.2999999999999998</v>
       </c>
       <c r="H10" s="0">
-        <v>7.4500000000000002</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="I10" s="0">
-        <v>79.989999999999995</v>
+        <v>83.989999999999995</v>
       </c>
       <c r="J10" s="0">
-        <v>462</v>
+        <v>1001</v>
       </c>
       <c r="K10" s="0">
-        <v>1806.5999999999999</v>
+        <v>6051.0900000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>23.920000000000002</v>
+        <v>35.899999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="11">
@@ -644,40 +611,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>5067144079</v>
+        <v>13491461122</v>
       </c>
       <c r="C11" s="0">
-        <v>6079867352</v>
+        <v>15782774501</v>
       </c>
       <c r="D11" s="0">
-        <v>378808</v>
+        <v>701145</v>
       </c>
       <c r="E11" s="0">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="F11" s="0">
-        <v>60112</v>
+        <v>70918</v>
       </c>
       <c r="G11" s="0">
-        <v>3.75</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>9.7100000000000009</v>
+        <v>10.57</v>
       </c>
       <c r="I11" s="0">
-        <v>83.340000000000003</v>
+        <v>85.480000000000004</v>
       </c>
       <c r="J11" s="0">
-        <v>928</v>
+        <v>1308</v>
       </c>
       <c r="K11" s="0">
-        <v>5072</v>
+        <v>5827.1099999999997</v>
       </c>
       <c r="L11" s="0">
-        <v>46.549999999999997</v>
+        <v>34.25</v>
       </c>
       <c r="M11" s="0">
-        <v>0.13</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="12">
@@ -685,40 +652,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>3573936749</v>
+        <v>1700736906</v>
       </c>
       <c r="C12" s="0">
-        <v>4416179862</v>
+        <v>1966454620</v>
       </c>
       <c r="D12" s="0">
-        <v>571304</v>
+        <v>447940</v>
       </c>
       <c r="E12" s="0">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="F12" s="0">
-        <v>32224</v>
+        <v>11631</v>
       </c>
       <c r="G12" s="0">
-        <v>4.1699999999999999</v>
+        <v>2.6499999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>11.449999999999999</v>
+        <v>6.6399999999999997</v>
       </c>
       <c r="I12" s="0">
-        <v>80.930000000000007</v>
+        <v>86.489999999999995</v>
       </c>
       <c r="J12" s="0">
-        <v>1022</v>
+        <v>945</v>
       </c>
       <c r="K12" s="0">
-        <v>4544.6199999999999</v>
+        <v>5004.1999999999998</v>
       </c>
       <c r="L12" s="0">
-        <v>33.920000000000002</v>
+        <v>27.960000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="13">
@@ -726,40 +693,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>39349587341</v>
+        <v>61916712277</v>
       </c>
       <c r="C13" s="0">
-        <v>47343104948</v>
+        <v>71479409750</v>
       </c>
       <c r="D13" s="0">
-        <v>389175</v>
+        <v>673318</v>
       </c>
       <c r="E13" s="0">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="F13" s="0">
-        <v>443965</v>
+        <v>323206</v>
       </c>
       <c r="G13" s="0">
-        <v>3.6499999999999999</v>
+        <v>3.04</v>
       </c>
       <c r="H13" s="0">
-        <v>8.3499999999999996</v>
+        <v>9.4100000000000001</v>
       </c>
       <c r="I13" s="0">
-        <v>83.120000000000005</v>
+        <v>86.620000000000005</v>
       </c>
       <c r="J13" s="0">
-        <v>807</v>
+        <v>1232</v>
       </c>
       <c r="K13" s="0">
-        <v>5391.5299999999997</v>
+        <v>6004.2399999999998</v>
       </c>
       <c r="L13" s="0">
-        <v>40.829999999999998</v>
+        <v>33.460000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.11600000000000001</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="14">
@@ -767,40 +734,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>83578335923</v>
+        <v>9459184413</v>
       </c>
       <c r="C14" s="0">
-        <v>101045400311</v>
+        <v>11004557704</v>
       </c>
       <c r="D14" s="0">
-        <v>539657</v>
+        <v>861751</v>
       </c>
       <c r="E14" s="0">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="F14" s="0">
-        <v>639310</v>
+        <v>39409</v>
       </c>
       <c r="G14" s="0">
-        <v>3.4100000000000001</v>
+        <v>3.0899999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>8.8800000000000008</v>
+        <v>11.529999999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>82.709999999999994</v>
+        <v>85.959999999999994</v>
       </c>
       <c r="J14" s="0">
-        <v>964</v>
+        <v>1560</v>
       </c>
       <c r="K14" s="0">
-        <v>5828.9799999999996</v>
+        <v>5172.1300000000001</v>
       </c>
       <c r="L14" s="0">
-        <v>35.609999999999999</v>
+        <v>28.890000000000001</v>
       </c>
       <c r="M14" s="0">
-        <v>0.096000000000000002</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="15">
@@ -808,40 +775,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>30680565244</v>
+        <v>23733255313</v>
       </c>
       <c r="C15" s="0">
-        <v>37504083148</v>
+        <v>27734987977</v>
       </c>
       <c r="D15" s="0">
-        <v>744129</v>
+        <v>548122</v>
       </c>
       <c r="E15" s="0">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F15" s="0">
-        <v>195899</v>
+        <v>125762</v>
       </c>
       <c r="G15" s="0">
-        <v>3.8900000000000001</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H15" s="0">
-        <v>10.84</v>
+        <v>7.4900000000000002</v>
       </c>
       <c r="I15" s="0">
-        <v>81.810000000000002</v>
+        <v>85.569999999999993</v>
       </c>
       <c r="J15" s="0">
-        <v>1039</v>
+        <v>1198</v>
       </c>
       <c r="K15" s="0">
-        <v>5113.46</v>
+        <v>7123.4399999999996</v>
       </c>
       <c r="L15" s="0">
-        <v>27.739999999999998</v>
+        <v>38.579999999999998</v>
       </c>
       <c r="M15" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="16">
@@ -849,40 +816,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>109257934645</v>
+        <v>8229152679</v>
       </c>
       <c r="C16" s="0">
-        <v>127496473953</v>
+        <v>9484767210</v>
       </c>
       <c r="D16" s="0">
-        <v>766205</v>
+        <v>706764</v>
       </c>
       <c r="E16" s="0">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="F16" s="0">
-        <v>590868</v>
+        <v>28521</v>
       </c>
       <c r="G16" s="0">
-        <v>3.5499999999999998</v>
+        <v>2.1299999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>10.57</v>
+        <v>7.3399999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>85.689999999999998</v>
+        <v>86.760000000000005</v>
       </c>
       <c r="J16" s="0">
-        <v>1152</v>
+        <v>1421</v>
       </c>
       <c r="K16" s="0">
-        <v>6355.1099999999997</v>
+        <v>7996.4700000000003</v>
       </c>
       <c r="L16" s="0">
-        <v>33.740000000000002</v>
+        <v>34.18</v>
       </c>
       <c r="M16" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="17">
@@ -890,40 +857,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>31642205471</v>
+        <v>22253940603</v>
       </c>
       <c r="C17" s="0">
-        <v>37519801450</v>
+        <v>26525705951</v>
       </c>
       <c r="D17" s="0">
-        <v>916011</v>
+        <v>909661</v>
       </c>
       <c r="E17" s="0">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F17" s="0">
-        <v>103742</v>
+        <v>43583</v>
       </c>
       <c r="G17" s="0">
-        <v>2.5299999999999998</v>
+        <v>1.49</v>
       </c>
       <c r="H17" s="0">
-        <v>11.109999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="I17" s="0">
-        <v>84.329999999999998</v>
+        <v>83.900000000000006</v>
       </c>
       <c r="J17" s="0">
-        <v>1880</v>
+        <v>3018</v>
       </c>
       <c r="K17" s="0">
-        <v>6480.04</v>
+        <v>9293.0699999999997</v>
       </c>
       <c r="L17" s="0">
-        <v>33.649999999999999</v>
+        <v>46.039999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -931,40 +898,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>5511285241</v>
+        <v>10769888047</v>
       </c>
       <c r="C18" s="0">
-        <v>6596500213</v>
+        <v>13099503841</v>
       </c>
       <c r="D18" s="0">
-        <v>225444</v>
+        <v>977575</v>
       </c>
       <c r="E18" s="0">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="F18" s="0">
-        <v>168809</v>
+        <v>17201</v>
       </c>
       <c r="G18" s="0">
-        <v>5.7699999999999996</v>
+        <v>1.28</v>
       </c>
       <c r="H18" s="0">
-        <v>7.2400000000000002</v>
+        <v>8.8499999999999996</v>
       </c>
       <c r="I18" s="0">
-        <v>83.549999999999997</v>
+        <v>82.219999999999999</v>
       </c>
       <c r="J18" s="0">
-        <v>349</v>
+        <v>3214</v>
       </c>
       <c r="K18" s="0">
-        <v>5566.3900000000003</v>
+        <v>9419.9899999999998</v>
       </c>
       <c r="L18" s="0">
-        <v>49.270000000000003</v>
+        <v>39.75</v>
       </c>
       <c r="M18" s="0">
-        <v>0.17899999999999999</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="19">
@@ -972,40 +939,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>196930</v>
+        <v>4189190066</v>
       </c>
       <c r="C19" s="0">
-        <v>359730</v>
+        <v>5300029226</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>1341780</v>
       </c>
       <c r="E19" s="0">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="F19" s="0">
-        <v>2</v>
+        <v>6327</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>12.57</v>
       </c>
       <c r="I19" s="0">
-        <v>54.740000000000002</v>
+        <v>79.040000000000006</v>
       </c>
       <c r="J19" s="0">
-        <v>1428</v>
+        <v>3766</v>
       </c>
       <c r="K19" s="0">
-        <v>2155466.3300000001</v>
+        <v>10172.24</v>
       </c>
       <c r="L19" s="0">
-        <v>17106.880000000001</v>
+        <v>45.729999999999997</v>
       </c>
       <c r="M19" s="0">
-        <v>39.146999999999998</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1013,40 +980,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>69615629790</v>
+        <v>16033296402</v>
       </c>
       <c r="C20" s="0">
-        <v>83964293367</v>
+        <v>19605485206</v>
       </c>
       <c r="D20" s="0">
-        <v>467820</v>
+        <v>1759918</v>
       </c>
       <c r="E20" s="0">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="F20" s="0">
-        <v>862716</v>
+        <v>17725</v>
       </c>
       <c r="G20" s="0">
-        <v>4.8099999999999996</v>
+        <v>1.5900000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>9.2699999999999996</v>
+        <v>12.84</v>
       </c>
       <c r="I20" s="0">
-        <v>82.909999999999997</v>
+        <v>81.780000000000001</v>
       </c>
       <c r="J20" s="0">
-        <v>689</v>
+        <v>3877</v>
       </c>
       <c r="K20" s="0">
-        <v>5029.8500000000004</v>
+        <v>10316.07</v>
       </c>
       <c r="L20" s="0">
-        <v>35.609999999999999</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="M20" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="21">
@@ -1054,40 +1021,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>145460307738</v>
+        <v>8195248673</v>
       </c>
       <c r="C21" s="0">
-        <v>173744007387</v>
+        <v>10061535222</v>
       </c>
       <c r="D21" s="0">
-        <v>584406</v>
+        <v>1771397</v>
       </c>
       <c r="E21" s="0">
-        <v>171</v>
+        <v>281</v>
       </c>
       <c r="F21" s="0">
-        <v>1067771</v>
+        <v>8118</v>
       </c>
       <c r="G21" s="0">
-        <v>3.5899999999999999</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H21" s="0">
-        <v>9.1300000000000008</v>
+        <v>12.98</v>
       </c>
       <c r="I21" s="0">
-        <v>83.719999999999999</v>
+        <v>81.450000000000003</v>
       </c>
       <c r="J21" s="0">
-        <v>956</v>
+        <v>4418</v>
       </c>
       <c r="K21" s="0">
-        <v>5676.4399999999996</v>
+        <v>9914.2700000000004</v>
       </c>
       <c r="L21" s="0">
-        <v>33.340000000000003</v>
+        <v>35.340000000000003</v>
       </c>
       <c r="M21" s="0">
-        <v>0.088999999999999996</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="22">
@@ -1095,40 +1062,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>32063929404</v>
+        <v>10407008850</v>
       </c>
       <c r="C22" s="0">
-        <v>38112249151</v>
+        <v>13811522615</v>
       </c>
       <c r="D22" s="0">
-        <v>702789</v>
+        <v>1466191</v>
       </c>
       <c r="E22" s="0">
-        <v>173</v>
+        <v>307</v>
       </c>
       <c r="F22" s="0">
-        <v>209021</v>
+        <v>8971</v>
       </c>
       <c r="G22" s="0">
-        <v>3.8500000000000001</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="H22" s="0">
-        <v>10.460000000000001</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="I22" s="0">
-        <v>84.129999999999995</v>
+        <v>75.349999999999994</v>
       </c>
       <c r="J22" s="0">
-        <v>1054</v>
+        <v>5038</v>
       </c>
       <c r="K22" s="0">
-        <v>5091.5600000000004</v>
+        <v>10970.559999999999</v>
       </c>
       <c r="L22" s="0">
-        <v>29.440000000000001</v>
+        <v>35.890000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="23">
@@ -1136,40 +1103,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>3550385308</v>
+        <v>14621513383</v>
       </c>
       <c r="C23" s="0">
-        <v>4220746656</v>
+        <v>18069637897</v>
       </c>
       <c r="D23" s="0">
-        <v>481271</v>
+        <v>1299039</v>
       </c>
       <c r="E23" s="0">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="F23" s="0">
-        <v>24605</v>
+        <v>20544</v>
       </c>
       <c r="G23" s="0">
-        <v>2.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="H23" s="0">
-        <v>7.2699999999999996</v>
+        <v>11.18</v>
       </c>
       <c r="I23" s="0">
-        <v>84.120000000000005</v>
+        <v>80.920000000000002</v>
       </c>
       <c r="J23" s="0">
-        <v>961</v>
+        <v>3729</v>
       </c>
       <c r="K23" s="0">
-        <v>5865.4899999999998</v>
+        <v>11865.719999999999</v>
       </c>
       <c r="L23" s="0">
-        <v>32.869999999999997</v>
+        <v>50.310000000000002</v>
       </c>
       <c r="M23" s="0">
-        <v>0.088999999999999996</v>
+        <v>0.10199999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1177,40 +1144,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>81635074793</v>
+        <v>29071138713</v>
       </c>
       <c r="C24" s="0">
-        <v>94698340468</v>
+        <v>37474068973</v>
       </c>
       <c r="D24" s="0">
-        <v>701417</v>
+        <v>1712709</v>
       </c>
       <c r="E24" s="0">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="F24" s="0">
-        <v>408462</v>
+        <v>29112</v>
       </c>
       <c r="G24" s="0">
-        <v>3.0299999999999998</v>
+        <v>1.3300000000000001</v>
       </c>
       <c r="H24" s="0">
-        <v>9.7799999999999994</v>
+        <v>12.859999999999999</v>
       </c>
       <c r="I24" s="0">
-        <v>86.209999999999994</v>
+        <v>77.579999999999998</v>
       </c>
       <c r="J24" s="0">
-        <v>1294</v>
+        <v>4872</v>
       </c>
       <c r="K24" s="0">
-        <v>5743.8100000000004</v>
+        <v>11515.91</v>
       </c>
       <c r="L24" s="0">
-        <v>32.07</v>
+        <v>43.57</v>
       </c>
       <c r="M24" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="25">
@@ -1218,40 +1185,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>16119529387</v>
+        <v>8471648174</v>
       </c>
       <c r="C25" s="0">
-        <v>18601111942</v>
+        <v>9948819528</v>
       </c>
       <c r="D25" s="0">
-        <v>845505</v>
+        <v>1962292</v>
       </c>
       <c r="E25" s="0">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="F25" s="0">
-        <v>65674</v>
+        <v>8088</v>
       </c>
       <c r="G25" s="0">
-        <v>2.9900000000000002</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="H25" s="0">
-        <v>11.43</v>
+        <v>12.470000000000001</v>
       </c>
       <c r="I25" s="0">
-        <v>86.659999999999997</v>
+        <v>85.150000000000006</v>
       </c>
       <c r="J25" s="0">
-        <v>1586</v>
+        <v>3868</v>
       </c>
       <c r="K25" s="0">
-        <v>4806.29</v>
+        <v>10131.299999999999</v>
       </c>
       <c r="L25" s="0">
-        <v>26.91</v>
+        <v>31.859999999999999</v>
       </c>
       <c r="M25" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1259,40 +1226,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>23733255313</v>
+        <v>39247149691</v>
       </c>
       <c r="C26" s="0">
-        <v>27734987977</v>
+        <v>48373572968</v>
       </c>
       <c r="D26" s="0">
-        <v>548122</v>
+        <v>1141963</v>
       </c>
       <c r="E26" s="0">
-        <v>187</v>
+        <v>289</v>
       </c>
       <c r="F26" s="0">
-        <v>125762</v>
+        <v>48332</v>
       </c>
       <c r="G26" s="0">
-        <v>2.4900000000000002</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="H26" s="0">
-        <v>7.4900000000000002</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="I26" s="0">
-        <v>85.569999999999993</v>
+        <v>81.129999999999995</v>
       </c>
       <c r="J26" s="0">
-        <v>1198</v>
+        <v>3552</v>
       </c>
       <c r="K26" s="0">
-        <v>7123.4399999999996</v>
+        <v>14424.07</v>
       </c>
       <c r="L26" s="0">
-        <v>38.579999999999998</v>
+        <v>51.07</v>
       </c>
       <c r="M26" s="0">
-        <v>0.097000000000000003</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="27">
@@ -1300,40 +1267,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>8229152679</v>
+        <v>23300085420</v>
       </c>
       <c r="C27" s="0">
-        <v>9484767210</v>
+        <v>29896544314</v>
       </c>
       <c r="D27" s="0">
-        <v>706764</v>
+        <v>1947658</v>
       </c>
       <c r="E27" s="0">
-        <v>234</v>
+        <v>330</v>
       </c>
       <c r="F27" s="0">
-        <v>28521</v>
+        <v>21718</v>
       </c>
       <c r="G27" s="0">
-        <v>2.1299999999999999</v>
+        <v>1.4099999999999999</v>
       </c>
       <c r="H27" s="0">
-        <v>7.3399999999999999</v>
+        <v>12</v>
       </c>
       <c r="I27" s="0">
-        <v>86.760000000000005</v>
+        <v>77.939999999999998</v>
       </c>
       <c r="J27" s="0">
-        <v>1421</v>
+        <v>4187</v>
       </c>
       <c r="K27" s="0">
-        <v>7996.4700000000003</v>
+        <v>15152.51</v>
       </c>
       <c r="L27" s="0">
-        <v>34.18</v>
+        <v>46.109999999999999</v>
       </c>
       <c r="M27" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1341,491 +1308,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>22253940603</v>
+        <v>563551473515</v>
       </c>
       <c r="C28" s="0">
-        <v>26525705951</v>
+        <v>673983598597</v>
       </c>
       <c r="D28" s="0">
-        <v>909661</v>
+        <v>716714</v>
       </c>
       <c r="E28" s="0">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="F28" s="0">
-        <v>43583</v>
+        <v>2826353</v>
       </c>
       <c r="G28" s="0">
-        <v>1.49</v>
+        <v>3.0099999999999998</v>
       </c>
       <c r="H28" s="0">
-        <v>9.7899999999999991</v>
+        <v>9.3599999999999994</v>
       </c>
       <c r="I28" s="0">
-        <v>83.900000000000006</v>
+        <v>83.620000000000005</v>
       </c>
       <c r="J28" s="0">
-        <v>3018</v>
+        <v>1244</v>
       </c>
       <c r="K28" s="0">
-        <v>9294.6900000000005</v>
+        <v>7310.6400000000003</v>
       </c>
       <c r="L28" s="0">
-        <v>46.049999999999997</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="M28" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="0">
-        <v>10769888047</v>
-      </c>
-      <c r="C29" s="0">
-        <v>13099503841</v>
-      </c>
-      <c r="D29" s="0">
-        <v>977575</v>
-      </c>
-      <c r="E29" s="0">
-        <v>237</v>
-      </c>
-      <c r="F29" s="0">
-        <v>17201</v>
-      </c>
-      <c r="G29" s="0">
-        <v>1.28</v>
-      </c>
-      <c r="H29" s="0">
-        <v>8.8499999999999996</v>
-      </c>
-      <c r="I29" s="0">
-        <v>82.219999999999999</v>
-      </c>
-      <c r="J29" s="0">
-        <v>3214</v>
-      </c>
-      <c r="K29" s="0">
-        <v>9419.9899999999998</v>
-      </c>
-      <c r="L29" s="0">
-        <v>39.75</v>
-      </c>
-      <c r="M29" s="0">
-        <v>0.085000000000000006</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="0">
-        <v>14204654018</v>
-      </c>
-      <c r="C30" s="0">
-        <v>17805230856</v>
-      </c>
-      <c r="D30" s="0">
-        <v>1400884</v>
-      </c>
-      <c r="E30" s="0">
-        <v>261</v>
-      </c>
-      <c r="F30" s="0">
-        <v>20891</v>
-      </c>
-      <c r="G30" s="0">
-        <v>1.6399999999999999</v>
-      </c>
-      <c r="H30" s="0">
-        <v>11.49</v>
-      </c>
-      <c r="I30" s="0">
-        <v>79.780000000000001</v>
-      </c>
-      <c r="J30" s="0">
-        <v>3298</v>
-      </c>
-      <c r="K30" s="0">
-        <v>10669.639999999999</v>
-      </c>
-      <c r="L30" s="0">
-        <v>41.229999999999997</v>
-      </c>
-      <c r="M30" s="0">
-        <v>0.086999999999999994</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0">
-        <v>16033296402</v>
-      </c>
-      <c r="C31" s="0">
-        <v>19605485206</v>
-      </c>
-      <c r="D31" s="0">
-        <v>1759918</v>
-      </c>
-      <c r="E31" s="0">
-        <v>286</v>
-      </c>
-      <c r="F31" s="0">
-        <v>17725</v>
-      </c>
-      <c r="G31" s="0">
-        <v>1.5900000000000001</v>
-      </c>
-      <c r="H31" s="0">
-        <v>12.84</v>
-      </c>
-      <c r="I31" s="0">
-        <v>81.780000000000001</v>
-      </c>
-      <c r="J31" s="0">
-        <v>3877</v>
-      </c>
-      <c r="K31" s="0">
-        <v>10316.07</v>
-      </c>
-      <c r="L31" s="0">
-        <v>36.159999999999997</v>
-      </c>
-      <c r="M31" s="0">
-        <v>0.074999999999999997</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="0">
-        <v>8195248673</v>
-      </c>
-      <c r="C32" s="0">
-        <v>10061535222</v>
-      </c>
-      <c r="D32" s="0">
-        <v>1771397</v>
-      </c>
-      <c r="E32" s="0">
-        <v>281</v>
-      </c>
-      <c r="F32" s="0">
-        <v>8118</v>
-      </c>
-      <c r="G32" s="0">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="H32" s="0">
-        <v>12.98</v>
-      </c>
-      <c r="I32" s="0">
-        <v>81.450000000000003</v>
-      </c>
-      <c r="J32" s="0">
-        <v>4418</v>
-      </c>
-      <c r="K32" s="0">
-        <v>9914.2700000000004</v>
-      </c>
-      <c r="L32" s="0">
-        <v>35.340000000000003</v>
-      </c>
-      <c r="M32" s="0">
-        <v>0.072999999999999995</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="0">
-        <v>10407008850</v>
-      </c>
-      <c r="C33" s="0">
-        <v>13811522615</v>
-      </c>
-      <c r="D33" s="0">
-        <v>1466191</v>
-      </c>
-      <c r="E33" s="0">
-        <v>307</v>
-      </c>
-      <c r="F33" s="0">
-        <v>8971</v>
-      </c>
-      <c r="G33" s="0">
-        <v>0.94999999999999996</v>
-      </c>
-      <c r="H33" s="0">
-        <v>9.5299999999999994</v>
-      </c>
-      <c r="I33" s="0">
-        <v>75.349999999999994</v>
-      </c>
-      <c r="J33" s="0">
-        <v>5038</v>
-      </c>
-      <c r="K33" s="0">
-        <v>10970.559999999999</v>
-      </c>
-      <c r="L33" s="0">
-        <v>35.890000000000001</v>
-      </c>
-      <c r="M33" s="0">
-        <v>0.070999999999999994</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="0">
-        <v>14621513383</v>
-      </c>
-      <c r="C34" s="0">
-        <v>18069637897</v>
-      </c>
-      <c r="D34" s="0">
-        <v>1299039</v>
-      </c>
-      <c r="E34" s="0">
-        <v>236</v>
-      </c>
-      <c r="F34" s="0">
-        <v>20544</v>
-      </c>
-      <c r="G34" s="0">
-        <v>1.48</v>
-      </c>
-      <c r="H34" s="0">
-        <v>11.18</v>
-      </c>
-      <c r="I34" s="0">
-        <v>80.920000000000002</v>
-      </c>
-      <c r="J34" s="0">
-        <v>3729</v>
-      </c>
-      <c r="K34" s="0">
-        <v>11865.719999999999</v>
-      </c>
-      <c r="L34" s="0">
-        <v>50.310000000000002</v>
-      </c>
-      <c r="M34" s="0">
-        <v>0.10199999999999999</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="0">
-        <v>29071138713</v>
-      </c>
-      <c r="C35" s="0">
-        <v>37474068973</v>
-      </c>
-      <c r="D35" s="0">
-        <v>1712709</v>
-      </c>
-      <c r="E35" s="0">
-        <v>266</v>
-      </c>
-      <c r="F35" s="0">
-        <v>29112</v>
-      </c>
-      <c r="G35" s="0">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="H35" s="0">
-        <v>12.859999999999999</v>
-      </c>
-      <c r="I35" s="0">
-        <v>77.579999999999998</v>
-      </c>
-      <c r="J35" s="0">
-        <v>4872</v>
-      </c>
-      <c r="K35" s="0">
-        <v>11515.91</v>
-      </c>
-      <c r="L35" s="0">
-        <v>43.57</v>
-      </c>
-      <c r="M35" s="0">
-        <v>0.085999999999999993</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="0">
-        <v>8471648174</v>
-      </c>
-      <c r="C36" s="0">
-        <v>9948819528</v>
-      </c>
-      <c r="D36" s="0">
-        <v>1962292</v>
-      </c>
-      <c r="E36" s="0">
-        <v>318</v>
-      </c>
-      <c r="F36" s="0">
-        <v>8088</v>
-      </c>
-      <c r="G36" s="0">
-        <v>1.6000000000000001</v>
-      </c>
-      <c r="H36" s="0">
-        <v>12.470000000000001</v>
-      </c>
-      <c r="I36" s="0">
-        <v>85.150000000000006</v>
-      </c>
-      <c r="J36" s="0">
-        <v>3868</v>
-      </c>
-      <c r="K36" s="0">
-        <v>10133.42</v>
-      </c>
-      <c r="L36" s="0">
-        <v>31.870000000000001</v>
-      </c>
-      <c r="M36" s="0">
-        <v>0.064000000000000001</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="0">
-        <v>39247149691</v>
-      </c>
-      <c r="C37" s="0">
-        <v>48373572968</v>
-      </c>
-      <c r="D37" s="0">
-        <v>1141963</v>
-      </c>
-      <c r="E37" s="0">
-        <v>289</v>
-      </c>
-      <c r="F37" s="0">
-        <v>48332</v>
-      </c>
-      <c r="G37" s="0">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="H37" s="0">
-        <v>8.3699999999999992</v>
-      </c>
-      <c r="I37" s="0">
-        <v>81.129999999999995</v>
-      </c>
-      <c r="J37" s="0">
-        <v>3552</v>
-      </c>
-      <c r="K37" s="0">
-        <v>14424.07</v>
-      </c>
-      <c r="L37" s="0">
-        <v>51.07</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.106</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="0">
-        <v>23300085420</v>
-      </c>
-      <c r="C38" s="0">
-        <v>29896544314</v>
-      </c>
-      <c r="D38" s="0">
-        <v>1947658</v>
-      </c>
-      <c r="E38" s="0">
-        <v>330</v>
-      </c>
-      <c r="F38" s="0">
-        <v>21718</v>
-      </c>
-      <c r="G38" s="0">
-        <v>1.4099999999999999</v>
-      </c>
-      <c r="H38" s="0">
-        <v>12</v>
-      </c>
-      <c r="I38" s="0">
-        <v>77.939999999999998</v>
-      </c>
-      <c r="J38" s="0">
-        <v>4187</v>
-      </c>
-      <c r="K38" s="0">
-        <v>15152.51</v>
-      </c>
-      <c r="L38" s="0">
-        <v>46.109999999999999</v>
-      </c>
-      <c r="M38" s="0">
-        <v>0.092999999999999999</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="0">
-        <v>947327538164</v>
-      </c>
-      <c r="C39" s="0">
-        <v>1140638877437</v>
-      </c>
-      <c r="D39" s="0">
-        <v>503807</v>
-      </c>
-      <c r="E39" s="0">
-        <v>138</v>
-      </c>
-      <c r="F39" s="0">
-        <v>7567440</v>
-      </c>
-      <c r="G39" s="0">
-        <v>3.3399999999999999</v>
-      </c>
-      <c r="H39" s="0">
-        <v>8.2799999999999994</v>
-      </c>
-      <c r="I39" s="0">
-        <v>83.049999999999997</v>
-      </c>
-      <c r="J39" s="0">
-        <v>911</v>
-      </c>
-      <c r="K39" s="0">
-        <v>5521.6800000000003</v>
-      </c>
-      <c r="L39" s="0">
-        <v>35.240000000000002</v>
-      </c>
-      <c r="M39" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
   </sheetData>
